--- a/datos_limpios/arg_tasas_est_prov.xlsx
+++ b/datos_limpios/arg_tasas_est_prov.xlsx
@@ -452,22 +452,22 @@
         <v>191.9749520851191</v>
       </c>
       <c r="H2">
-        <v>859.2880856746347</v>
+        <v>676.1996596107617</v>
       </c>
       <c r="I2">
-        <v>567.5864975152851</v>
+        <v>451.5530213930774</v>
       </c>
       <c r="J2">
-        <v>1150.010463581991</v>
+        <v>900.3161071967969</v>
       </c>
       <c r="K2">
-        <v>1031.745015263803</v>
+        <v>848.9770685595711</v>
       </c>
       <c r="L2">
-        <v>740.0750401685186</v>
+        <v>624.7396252216843</v>
       </c>
       <c r="M2">
-        <v>1323.151804674017</v>
+        <v>1072.403968909008</v>
       </c>
     </row>
     <row r="3">
@@ -501,22 +501,22 @@
         <v>250.5341903576754</v>
       </c>
       <c r="H3">
-        <v>2068.93988855828</v>
+        <v>1493.170333159748</v>
       </c>
       <c r="I3">
-        <v>1461.498242142027</v>
+        <v>1056.154931893742</v>
       </c>
       <c r="J3">
-        <v>2728.468345449111</v>
+        <v>1946.135869917465</v>
       </c>
       <c r="K3">
-        <v>2293.291482321041</v>
+        <v>1718.410305602295</v>
       </c>
       <c r="L3">
-        <v>1680.869017790021</v>
+        <v>1279.23663534295</v>
       </c>
       <c r="M3">
-        <v>2951.164601694407</v>
+        <v>2171.90696013485</v>
       </c>
     </row>
     <row r="4">
@@ -550,22 +550,22 @@
         <v>535.6757454940068</v>
       </c>
       <c r="H4">
-        <v>1286.153410157144</v>
+        <v>1029.537957543909</v>
       </c>
       <c r="I4">
-        <v>1016.640080729335</v>
+        <v>814.0977208545831</v>
       </c>
       <c r="J4">
-        <v>1558.646204500312</v>
+        <v>1247.442733421509</v>
       </c>
       <c r="K4">
-        <v>1804.633506687993</v>
+        <v>1546.786916132174</v>
       </c>
       <c r="L4">
-        <v>1530.909252715662</v>
+        <v>1330.69559328476</v>
       </c>
       <c r="M4">
-        <v>2076.583892590167</v>
+        <v>1764.089971288735</v>
       </c>
     </row>
     <row r="5">
@@ -599,22 +599,22 @@
         <v>602.0157767567121</v>
       </c>
       <c r="H5">
-        <v>1845.303388113135</v>
+        <v>1324.754759937883</v>
       </c>
       <c r="I5">
-        <v>1329.591767273549</v>
+        <v>998.16930022849</v>
       </c>
       <c r="J5">
-        <v>2372.823607666146</v>
+        <v>1646.058488715548</v>
       </c>
       <c r="K5">
-        <v>2426.02889061832</v>
+        <v>1906.134139410055</v>
       </c>
       <c r="L5">
-        <v>1912.203190006545</v>
+        <v>1582.162625186046</v>
       </c>
       <c r="M5">
-        <v>2953.753341015915</v>
+        <v>2228.563299390154</v>
       </c>
     </row>
     <row r="6">
@@ -648,22 +648,22 @@
         <v>1202.088792920455</v>
       </c>
       <c r="H6">
-        <v>1152.551243354298</v>
+        <v>913.9587189715343</v>
       </c>
       <c r="I6">
-        <v>848.5564606838917</v>
+        <v>676.1786670987593</v>
       </c>
       <c r="J6">
-        <v>1454.62396496355</v>
+        <v>1149.815716629382</v>
       </c>
       <c r="K6">
-        <v>2148.172654440044</v>
+        <v>1910.76577200413</v>
       </c>
       <c r="L6">
-        <v>1790.550321721198</v>
+        <v>1603.169012629356</v>
       </c>
       <c r="M6">
-        <v>2517.304468881939</v>
+        <v>2225.321783734531</v>
       </c>
     </row>
     <row r="7">
@@ -697,22 +697,22 @@
         <v>1113.793991198968</v>
       </c>
       <c r="H7">
-        <v>901.2490553817545</v>
+        <v>785.0622938026169</v>
       </c>
       <c r="I7">
-        <v>583.0986194723254</v>
+        <v>506.5307713001196</v>
       </c>
       <c r="J7">
-        <v>1225.470129257518</v>
+        <v>1066.340433233549</v>
       </c>
       <c r="K7">
-        <v>1832.852052720929</v>
+        <v>1717.827818422969</v>
       </c>
       <c r="L7">
-        <v>1465.927085009107</v>
+        <v>1386.218273011766</v>
       </c>
       <c r="M7">
-        <v>2207.842688407647</v>
+        <v>2057.114690217817</v>
       </c>
     </row>
     <row r="8">
@@ -746,22 +746,22 @@
         <v>911.168959756068</v>
       </c>
       <c r="H8">
-        <v>1221.0892696272</v>
+        <v>975.3737357148106</v>
       </c>
       <c r="I8">
-        <v>876.6557947878766</v>
+        <v>699.13016731158</v>
       </c>
       <c r="J8">
-        <v>1562.067545907105</v>
+        <v>1245.480655958432</v>
       </c>
       <c r="K8">
-        <v>2081.483478229344</v>
+        <v>1834.740678067695</v>
       </c>
       <c r="L8">
-        <v>1732.681689214719</v>
+        <v>1553.600492915577</v>
       </c>
       <c r="M8">
-        <v>2424.367577413945</v>
+        <v>2112.647866227059</v>
       </c>
     </row>
     <row r="9">
@@ -795,22 +795,22 @@
         <v>1056.50502473097</v>
       </c>
       <c r="H9">
-        <v>1625.805849474727</v>
+        <v>1371.931454684592</v>
       </c>
       <c r="I9">
-        <v>1099.618995820862</v>
+        <v>925.3226072890368</v>
       </c>
       <c r="J9">
-        <v>2153.244650528318</v>
+        <v>1822.447651134884</v>
       </c>
       <c r="K9">
-        <v>2625.450724238141</v>
+        <v>2372.44061585557</v>
       </c>
       <c r="L9">
-        <v>2105.378258957155</v>
+        <v>1923.647622007416</v>
       </c>
       <c r="M9">
-        <v>3151.913006683596</v>
+        <v>2823.939061393761</v>
       </c>
     </row>
     <row r="10">
@@ -844,22 +844,22 @@
         <v>982.2433900947622</v>
       </c>
       <c r="H10">
-        <v>838.03736291686</v>
+        <v>668.2486199822022</v>
       </c>
       <c r="I10">
-        <v>588.3036251892195</v>
+        <v>469.5756146098182</v>
       </c>
       <c r="J10">
-        <v>1079.652690771983</v>
+        <v>859.2312459840815</v>
       </c>
       <c r="K10">
-        <v>1710.001433239361</v>
+        <v>1540.046078502029</v>
       </c>
       <c r="L10">
-        <v>1441.037843369807</v>
+        <v>1318.434041983009</v>
       </c>
       <c r="M10">
-        <v>1974.438754706913</v>
+        <v>1761.850053886077</v>
       </c>
     </row>
     <row r="11">
@@ -893,22 +893,22 @@
         <v>931.8417294094864</v>
       </c>
       <c r="H11">
-        <v>1449.35076448484</v>
+        <v>1142.918680905156</v>
       </c>
       <c r="I11">
-        <v>967.5538755979658</v>
+        <v>760.5754830599219</v>
       </c>
       <c r="J11">
-        <v>1933.063494224987</v>
+        <v>1531.353982281167</v>
       </c>
       <c r="K11">
-        <v>2277.71586358143</v>
+        <v>1969.915916485194</v>
       </c>
       <c r="L11">
-        <v>1787.139793932932</v>
+        <v>1572.942590729842</v>
       </c>
       <c r="M11">
-        <v>2770.752460071216</v>
+        <v>2372.7302259774</v>
       </c>
     </row>
     <row r="12">
@@ -942,22 +942,22 @@
         <v>1205.221286171436</v>
       </c>
       <c r="H12">
-        <v>1326.181066206878</v>
+        <v>1062.854606532785</v>
       </c>
       <c r="I12">
-        <v>968.4857449310407</v>
+        <v>776.8755927980045</v>
       </c>
       <c r="J12">
-        <v>1675.780443694646</v>
+        <v>1342.261616247825</v>
       </c>
       <c r="K12">
-        <v>2406.006815252028</v>
+        <v>2142.411832268282</v>
       </c>
       <c r="L12">
-        <v>2028.708341687575</v>
+        <v>1835.590838889186</v>
       </c>
       <c r="M12">
-        <v>2788.604354001461</v>
+        <v>2456.23108561958</v>
       </c>
     </row>
     <row r="13">
@@ -991,22 +991,22 @@
         <v>983.5557012180114</v>
       </c>
       <c r="H13">
-        <v>1076.756989913383</v>
+        <v>866.3056429713586</v>
       </c>
       <c r="I13">
-        <v>739.8723766544956</v>
+        <v>589.1213146478585</v>
       </c>
       <c r="J13">
-        <v>1427.607329792549</v>
+        <v>1159.021942900828</v>
       </c>
       <c r="K13">
-        <v>1950.376843589856</v>
+        <v>1740.542800934407</v>
       </c>
       <c r="L13">
-        <v>1597.825810662018</v>
+        <v>1442.745044408582</v>
       </c>
       <c r="M13">
-        <v>2320.962068689574</v>
+        <v>2056.148567637047</v>
       </c>
     </row>
     <row r="14">
@@ -1040,22 +1040,22 @@
         <v>705.0351884284474</v>
       </c>
       <c r="H14">
-        <v>1596.002879888022</v>
+        <v>1298.086960366237</v>
       </c>
       <c r="I14">
-        <v>1161.316154385974</v>
+        <v>933.9729590623291</v>
       </c>
       <c r="J14">
-        <v>2074.635130024048</v>
+        <v>1704.005984430299</v>
       </c>
       <c r="K14">
-        <v>2175.975408612415</v>
+        <v>1877.573785726748</v>
       </c>
       <c r="L14">
-        <v>1714.266455220319</v>
+        <v>1487.098247967328</v>
       </c>
       <c r="M14">
-        <v>2669.334833935553</v>
+        <v>2296.980909775234</v>
       </c>
     </row>
     <row r="15">
@@ -1089,22 +1089,22 @@
         <v>776.4062132878473</v>
       </c>
       <c r="H15">
-        <v>1368.76895102291</v>
+        <v>1141.23727432103</v>
       </c>
       <c r="I15">
-        <v>979.4910369917385</v>
+        <v>814.1267240341367</v>
       </c>
       <c r="J15">
-        <v>1761.343327180722</v>
+        <v>1459.889999124216</v>
       </c>
       <c r="K15">
-        <v>2015.31277453793</v>
+        <v>1788.493553994673</v>
       </c>
       <c r="L15">
-        <v>1598.149909198751</v>
+        <v>1435.664742737598</v>
       </c>
       <c r="M15">
-        <v>2425.128657347343</v>
+        <v>2133.657616419653</v>
       </c>
     </row>
     <row r="16">
@@ -1138,22 +1138,22 @@
         <v>881.3288231059303</v>
       </c>
       <c r="H16">
-        <v>1103.538206887922</v>
+        <v>885.4856445281494</v>
       </c>
       <c r="I16">
-        <v>751.3405951533409</v>
+        <v>605.9229412824478</v>
       </c>
       <c r="J16">
-        <v>1452.373305759359</v>
+        <v>1160.490595132891</v>
       </c>
       <c r="K16">
-        <v>1900.702822841717</v>
+        <v>1682.411399105603</v>
       </c>
       <c r="L16">
-        <v>1536.630440013226</v>
+        <v>1390.279032015541</v>
       </c>
       <c r="M16">
-        <v>2263.881977918305</v>
+        <v>1971.779226650138</v>
       </c>
     </row>
     <row r="17">
@@ -1187,22 +1187,22 @@
         <v>901.8104579510023</v>
       </c>
       <c r="H17">
-        <v>1453.044326394535</v>
+        <v>1102.118388193386</v>
       </c>
       <c r="I17">
-        <v>935.9125030881551</v>
+        <v>714.0852789099679</v>
       </c>
       <c r="J17">
-        <v>1981.009484839633</v>
+        <v>1496.675631203431</v>
       </c>
       <c r="K17">
-        <v>2270.430314012468</v>
+        <v>1920.24688583082</v>
       </c>
       <c r="L17">
-        <v>1748.196247444828</v>
+        <v>1524.143796012553</v>
       </c>
       <c r="M17">
-        <v>2812.915848384976</v>
+        <v>2320.740626009959</v>
       </c>
     </row>
     <row r="18">
@@ -1236,22 +1236,22 @@
         <v>2027.041069376421</v>
       </c>
       <c r="H18">
-        <v>1364.270363052022</v>
+        <v>1099.139354546489</v>
       </c>
       <c r="I18">
-        <v>889.898933919766</v>
+        <v>722.6266558817315</v>
       </c>
       <c r="J18">
-        <v>1890.169552727208</v>
+        <v>1515.895791259039</v>
       </c>
       <c r="K18">
-        <v>3154.572598286729</v>
+        <v>2889.603611687381</v>
       </c>
       <c r="L18">
-        <v>2617.675638926009</v>
+        <v>2438.324223587026</v>
       </c>
       <c r="M18">
-        <v>3729.578199326132</v>
+        <v>3364.936123036827</v>
       </c>
     </row>
     <row r="19">
@@ -1285,22 +1285,22 @@
         <v>1300.303843634589</v>
       </c>
       <c r="H19">
-        <v>669.5147698469348</v>
+        <v>568.8541620624152</v>
       </c>
       <c r="I19">
-        <v>446.3880120385624</v>
+        <v>379.8534903431797</v>
       </c>
       <c r="J19">
-        <v>892.4508209383621</v>
+        <v>757.1063739895565</v>
       </c>
       <c r="K19">
-        <v>1793.406328943038</v>
+        <v>1693.217024717249</v>
       </c>
       <c r="L19">
-        <v>1515.117541219481</v>
+        <v>1442.003018347621</v>
       </c>
       <c r="M19">
-        <v>2075.237852039604</v>
+        <v>1949.42668742396</v>
       </c>
     </row>
     <row r="20">
@@ -1334,22 +1334,22 @@
         <v>817.9833397264474</v>
       </c>
       <c r="H20">
-        <v>509.0211725618019</v>
+        <v>413.1522443067519</v>
       </c>
       <c r="I20">
-        <v>351.9044784808106</v>
+        <v>285.4387761272489</v>
       </c>
       <c r="J20">
-        <v>670.530185692535</v>
+        <v>544.1600278110341</v>
       </c>
       <c r="K20">
-        <v>1204.888993945661</v>
+        <v>1109.100463816445</v>
       </c>
       <c r="L20">
-        <v>1003.905629896254</v>
+        <v>929.7485513311243</v>
       </c>
       <c r="M20">
-        <v>1406.838948811814</v>
+        <v>1287.360169769226</v>
       </c>
     </row>
     <row r="21">
@@ -1383,22 +1383,22 @@
         <v>698.1974396447506</v>
       </c>
       <c r="H21">
-        <v>1041.316097331171</v>
+        <v>826.4939488088432</v>
       </c>
       <c r="I21">
-        <v>679.0461439601004</v>
+        <v>532.8614832955997</v>
       </c>
       <c r="J21">
-        <v>1416.241708352537</v>
+        <v>1120.733204445142</v>
       </c>
       <c r="K21">
-        <v>1628.010628435481</v>
+        <v>1413.032989524177</v>
       </c>
       <c r="L21">
-        <v>1243.403369008709</v>
+        <v>1091.35688415501</v>
       </c>
       <c r="M21">
-        <v>2024.001596851191</v>
+        <v>1731.871706462069</v>
       </c>
     </row>
     <row r="22">
@@ -1432,22 +1432,22 @@
         <v>590.7274888766594</v>
       </c>
       <c r="H22">
-        <v>715.585659059001</v>
+        <v>571.4737937260372</v>
       </c>
       <c r="I22">
-        <v>500.4460033267088</v>
+        <v>402.3415486015897</v>
       </c>
       <c r="J22">
-        <v>936.4342886113121</v>
+        <v>744.3652168587155</v>
       </c>
       <c r="K22">
-        <v>1190.659626212533</v>
+        <v>1045.818911100205</v>
       </c>
       <c r="L22">
-        <v>948.8203396493687</v>
+        <v>842.1671501713518</v>
       </c>
       <c r="M22">
-        <v>1438.246387242176</v>
+        <v>1251.753583510505</v>
       </c>
     </row>
     <row r="23">
@@ -1481,22 +1481,22 @@
         <v>565.5737978641787</v>
       </c>
       <c r="H23">
-        <v>889.1104305514033</v>
+        <v>705.825774789581</v>
       </c>
       <c r="I23">
-        <v>557.1459690444484</v>
+        <v>434.0650704560613</v>
       </c>
       <c r="J23">
-        <v>1239.303939392123</v>
+        <v>990.7467492013775</v>
       </c>
       <c r="K23">
-        <v>1344.050393100184</v>
+        <v>1161.380662287012</v>
       </c>
       <c r="L23">
-        <v>986.9976861005897</v>
+        <v>860.5917427710169</v>
       </c>
       <c r="M23">
-        <v>1708.565813402235</v>
+        <v>1459.359617804213</v>
       </c>
     </row>
     <row r="24">
@@ -1530,22 +1530,22 @@
         <v>1105.815645011932</v>
       </c>
       <c r="H24">
-        <v>1416.289132864243</v>
+        <v>1155.02536016689</v>
       </c>
       <c r="I24">
-        <v>1041.324020896045</v>
+        <v>849.8686940619491</v>
       </c>
       <c r="J24">
-        <v>1804.193527822664</v>
+        <v>1469.566141648462</v>
       </c>
       <c r="K24">
-        <v>2316.437573272386</v>
+        <v>2055.360757027363</v>
       </c>
       <c r="L24">
-        <v>1893.070838185293</v>
+        <v>1690.530124094114</v>
       </c>
       <c r="M24">
-        <v>2752.093790003677</v>
+        <v>2426.512390797329</v>
       </c>
     </row>
     <row r="25">
@@ -1579,22 +1579,22 @@
         <v>972.9340419801335</v>
       </c>
       <c r="H25">
-        <v>1328.921851519068</v>
+        <v>1093.762508028952</v>
       </c>
       <c r="I25">
-        <v>875.3697336138003</v>
+        <v>723.6075749104858</v>
       </c>
       <c r="J25">
-        <v>1785.596161935257</v>
+        <v>1469.798318771453</v>
       </c>
       <c r="K25">
-        <v>2120.760557761543</v>
+        <v>1886.784182320849</v>
       </c>
       <c r="L25">
-        <v>1634.425273239172</v>
+        <v>1471.375197430359</v>
       </c>
       <c r="M25">
-        <v>2611.152135326038</v>
+        <v>2305.882997138777</v>
       </c>
     </row>
     <row r="26">
@@ -1628,22 +1628,22 @@
         <v>1346.219393945523</v>
       </c>
       <c r="H26">
-        <v>844.5911118287465</v>
+        <v>689.8725682180713</v>
       </c>
       <c r="I26">
-        <v>592.5798928076471</v>
+        <v>482.8787239904239</v>
       </c>
       <c r="J26">
-        <v>1100.107563150444</v>
+        <v>901.0319201810255</v>
       </c>
       <c r="K26">
-        <v>2102.376510567879</v>
+        <v>1948.93978184728</v>
       </c>
       <c r="L26">
-        <v>1833.765355981854</v>
+        <v>1722.46867716241</v>
       </c>
       <c r="M26">
-        <v>2373.735179337379</v>
+        <v>2176.623467331565</v>
       </c>
     </row>
     <row r="27">
@@ -1677,22 +1677,22 @@
         <v>1465.73443866058</v>
       </c>
       <c r="H27">
-        <v>1296.53104788581</v>
+        <v>850.7840073313567</v>
       </c>
       <c r="I27">
-        <v>851.7880076095241</v>
+        <v>563.9234111465703</v>
       </c>
       <c r="J27">
-        <v>1746.667420438363</v>
+        <v>1135.378725052731</v>
       </c>
       <c r="K27">
-        <v>2668.076769629371</v>
+        <v>2221.8288913233</v>
       </c>
       <c r="L27">
-        <v>2216.41053379448</v>
+        <v>1921.143323999833</v>
       </c>
       <c r="M27">
-        <v>3128.789989556725</v>
+        <v>2514.847154389157</v>
       </c>
     </row>
     <row r="28">
@@ -1726,22 +1726,22 @@
         <v>1554.206092684479</v>
       </c>
       <c r="H28">
-        <v>1005.739886872024</v>
+        <v>802.7936144500488</v>
       </c>
       <c r="I28">
-        <v>700.7643170511858</v>
+        <v>559.7605781446529</v>
       </c>
       <c r="J28">
-        <v>1328.69462397205</v>
+        <v>1058.623400537281</v>
       </c>
       <c r="K28">
-        <v>2405.485523287291</v>
+        <v>2201.336672317073</v>
       </c>
       <c r="L28">
-        <v>2063.956616110289</v>
+        <v>1914.001924195947</v>
       </c>
       <c r="M28">
-        <v>2765.26123098979</v>
+        <v>2505.349858968302</v>
       </c>
     </row>
     <row r="29">
@@ -1775,22 +1775,22 @@
         <v>1073.443833318844</v>
       </c>
       <c r="H29">
-        <v>1210.992290132206</v>
+        <v>872.6187533219327</v>
       </c>
       <c r="I29">
-        <v>819.9488928345413</v>
+        <v>601.4232157417032</v>
       </c>
       <c r="J29">
-        <v>1616.721634154551</v>
+        <v>1148.25294824391</v>
       </c>
       <c r="K29">
-        <v>2168.626948944707</v>
+        <v>1829.75882092491</v>
       </c>
       <c r="L29">
-        <v>1760.79647498462</v>
+        <v>1532.54016784489</v>
       </c>
       <c r="M29">
-        <v>2590.344152783814</v>
+        <v>2126.674068847551</v>
       </c>
     </row>
     <row r="30">
@@ -1824,22 +1824,22 @@
         <v>1480.415342883506</v>
       </c>
       <c r="H30">
-        <v>1232.286840008973</v>
+        <v>992.1917262055448</v>
       </c>
       <c r="I30">
-        <v>897.9614323626009</v>
+        <v>719.934241714994</v>
       </c>
       <c r="J30">
-        <v>1567.748124047854</v>
+        <v>1265.300725889678</v>
       </c>
       <c r="K30">
-        <v>2527.204745178478</v>
+        <v>2286.225407719277</v>
       </c>
       <c r="L30">
-        <v>2145.630051601528</v>
+        <v>1961.117205649748</v>
       </c>
       <c r="M30">
-        <v>2914.75652252927</v>
+        <v>2614.550466412269</v>
       </c>
     </row>
     <row r="31">
@@ -1873,22 +1873,22 @@
         <v>1503.969421336464</v>
       </c>
       <c r="H31">
-        <v>1350.669588235363</v>
+        <v>1201.546068433401</v>
       </c>
       <c r="I31">
-        <v>909.9477074452063</v>
+        <v>822.7369304854919</v>
       </c>
       <c r="J31">
-        <v>1784.747202430538</v>
+        <v>1573.498708942873</v>
       </c>
       <c r="K31">
-        <v>2670.689902507203</v>
+        <v>2523.248242291097</v>
       </c>
       <c r="L31">
-        <v>2198.287268460638</v>
+        <v>2104.785483314394</v>
       </c>
       <c r="M31">
-        <v>3139.862481126324</v>
+        <v>2934.610492132771</v>
       </c>
     </row>
     <row r="32">
@@ -1922,22 +1922,22 @@
         <v>631.8755407256842</v>
       </c>
       <c r="H32">
-        <v>1482.464137895041</v>
+        <v>1195.698822375193</v>
       </c>
       <c r="I32">
-        <v>1104.83109920621</v>
+        <v>898.3792102744496</v>
       </c>
       <c r="J32">
-        <v>1852.421673760829</v>
+        <v>1493.043359902344</v>
       </c>
       <c r="K32">
-        <v>2016.653214982258</v>
+        <v>1730.608959863497</v>
       </c>
       <c r="L32">
-        <v>1624.15643993783</v>
+        <v>1409.447795188106</v>
       </c>
       <c r="M32">
-        <v>2400.617534132412</v>
+        <v>2042.250197484646</v>
       </c>
     </row>
     <row r="33">
@@ -1971,22 +1971,22 @@
         <v>561.5137280097149</v>
       </c>
       <c r="H33">
-        <v>1777.369321925185</v>
+        <v>1228.967297071379</v>
       </c>
       <c r="I33">
-        <v>1116.021490636766</v>
+        <v>806.7348248506778</v>
       </c>
       <c r="J33">
-        <v>2587.788041866358</v>
+        <v>1660.827213035275</v>
       </c>
       <c r="K33">
-        <v>2250.11883933504</v>
+        <v>1700.405977908882</v>
       </c>
       <c r="L33">
-        <v>1576.658121890658</v>
+        <v>1267.473958511018</v>
       </c>
       <c r="M33">
-        <v>3062.273755137641</v>
+        <v>2139.520913390619</v>
       </c>
     </row>
     <row r="34">
@@ -2020,22 +2020,22 @@
         <v>585.5226989282233</v>
       </c>
       <c r="H34">
-        <v>716.3860863507915</v>
+        <v>589.465365473864</v>
       </c>
       <c r="I34">
-        <v>513.8384386378448</v>
+        <v>420.5084473350868</v>
       </c>
       <c r="J34">
-        <v>926.2596515146244</v>
+        <v>765.7355084694645</v>
       </c>
       <c r="K34">
-        <v>1222.615798062606</v>
+        <v>1096.169387773599</v>
       </c>
       <c r="L34">
-        <v>1003.262246794277</v>
+        <v>908.7604921907364</v>
       </c>
       <c r="M34">
-        <v>1443.372324647315</v>
+        <v>1284.225835845444</v>
       </c>
     </row>
     <row r="35">
@@ -2069,22 +2069,22 @@
         <v>567.6943599359585</v>
       </c>
       <c r="H35">
-        <v>734.2571466371285</v>
+        <v>557.379702739566</v>
       </c>
       <c r="I35">
-        <v>428.4446816660593</v>
+        <v>320.5307854046671</v>
       </c>
       <c r="J35">
-        <v>1064.22408764388</v>
+        <v>811.7864703934473</v>
       </c>
       <c r="K35">
-        <v>1222.783137032874</v>
+        <v>1046.325889840029</v>
       </c>
       <c r="L35">
-        <v>907.6118381785155</v>
+        <v>796.2364120203412</v>
       </c>
       <c r="M35">
-        <v>1564.172814251823</v>
+        <v>1313.128679880535</v>
       </c>
     </row>
     <row r="36">
@@ -2118,22 +2118,22 @@
         <v>1895.029880884426</v>
       </c>
       <c r="H36">
-        <v>1313.099600564136</v>
+        <v>1046.53283510639</v>
       </c>
       <c r="I36">
-        <v>997.3422821273344</v>
+        <v>796.4837129467911</v>
       </c>
       <c r="J36">
-        <v>1646.098804577631</v>
+        <v>1312.405120754918</v>
       </c>
       <c r="K36">
-        <v>3037.203371494265</v>
+        <v>2769.286383966953</v>
       </c>
       <c r="L36">
-        <v>2665.065838044487</v>
+        <v>2457.17598120584</v>
       </c>
       <c r="M36">
-        <v>3416.846166274023</v>
+        <v>3091.305286477659</v>
       </c>
     </row>
     <row r="37">
@@ -2167,22 +2167,22 @@
         <v>1691.369231841784</v>
       </c>
       <c r="H37">
-        <v>1794.959389318878</v>
+        <v>1199.259006102487</v>
       </c>
       <c r="I37">
-        <v>1148.925134390576</v>
+        <v>805.2193067751548</v>
       </c>
       <c r="J37">
-        <v>2489.253864804073</v>
+        <v>1598.929580386906</v>
       </c>
       <c r="K37">
-        <v>3321.787575296131</v>
+        <v>2728.628657977114</v>
       </c>
       <c r="L37">
-        <v>2656.344958630004</v>
+        <v>2298.243510902776</v>
       </c>
       <c r="M37">
-        <v>4030.210697339052</v>
+        <v>3166.589546982446</v>
       </c>
     </row>
     <row r="38">
@@ -2216,22 +2216,22 @@
         <v>1256.376575917743</v>
       </c>
       <c r="H38">
-        <v>1272.004319128914</v>
+        <v>1045.00140177748</v>
       </c>
       <c r="I38">
-        <v>980.3806965122077</v>
+        <v>799.9849195171911</v>
       </c>
       <c r="J38">
-        <v>1565.044816396346</v>
+        <v>1293.181517806374</v>
       </c>
       <c r="K38">
-        <v>2347.291603516064</v>
+        <v>2120.545011054223</v>
       </c>
       <c r="L38">
-        <v>2001.917628363989</v>
+        <v>1817.900533755531</v>
       </c>
       <c r="M38">
-        <v>2692.063936755329</v>
+        <v>2424.626131532107</v>
       </c>
     </row>
     <row r="39">
@@ -2265,22 +2265,22 @@
         <v>1410.024487939064</v>
       </c>
       <c r="H39">
-        <v>1114.111672295871</v>
+        <v>992.588339606496</v>
       </c>
       <c r="I39">
-        <v>725.7412780408205</v>
+        <v>656.9333434585711</v>
       </c>
       <c r="J39">
-        <v>1511.644892203314</v>
+        <v>1337.525602892749</v>
       </c>
       <c r="K39">
-        <v>2333.502458996666</v>
+        <v>2212.558119920182</v>
       </c>
       <c r="L39">
-        <v>1907.91010304095</v>
+        <v>1832.683183136406</v>
       </c>
       <c r="M39">
-        <v>2777.791899024011</v>
+        <v>2609.400953277931</v>
       </c>
     </row>
     <row r="40">
@@ -2314,22 +2314,22 @@
         <v>1271.918952843879</v>
       </c>
       <c r="H40">
-        <v>1288.589106095989</v>
+        <v>1041.825886016563</v>
       </c>
       <c r="I40">
-        <v>940.8319154458549</v>
+        <v>762.2220827364173</v>
       </c>
       <c r="J40">
-        <v>1666.608865352921</v>
+        <v>1341.036596116034</v>
       </c>
       <c r="K40">
-        <v>2294.288510470387</v>
+        <v>2047.437879068974</v>
       </c>
       <c r="L40">
-        <v>1844.480407145048</v>
+        <v>1648.340956660739</v>
       </c>
       <c r="M40">
-        <v>2749.905974593553</v>
+        <v>2439.143292142147</v>
       </c>
     </row>
     <row r="41">
@@ -2363,22 +2363,22 @@
         <v>1034.730427933544</v>
       </c>
       <c r="H41">
-        <v>1179.670033414008</v>
+        <v>1033.693957354775</v>
       </c>
       <c r="I41">
-        <v>781.5599413867208</v>
+        <v>687.8949589862592</v>
       </c>
       <c r="J41">
-        <v>1577.445547633224</v>
+        <v>1381.63110079242</v>
       </c>
       <c r="K41">
-        <v>2000.85399882822</v>
+        <v>1855.520667228674</v>
       </c>
       <c r="L41">
-        <v>1561.094220186524</v>
+        <v>1456.752791079934</v>
       </c>
       <c r="M41">
-        <v>2455.052108977433</v>
+        <v>2266.392325967345</v>
       </c>
     </row>
     <row r="42">
@@ -2412,22 +2412,22 @@
         <v>1002.132310653293</v>
       </c>
       <c r="H42">
-        <v>810.4786941049683</v>
+        <v>653.1188370630243</v>
       </c>
       <c r="I42">
-        <v>596.384384295661</v>
+        <v>481.7361625862831</v>
       </c>
       <c r="J42">
-        <v>1028.411151085349</v>
+        <v>828.6135982187981</v>
       </c>
       <c r="K42">
-        <v>1761.665275490393</v>
+        <v>1603.788279002391</v>
       </c>
       <c r="L42">
-        <v>1543.527198958911</v>
+        <v>1424.928929126338</v>
       </c>
       <c r="M42">
-        <v>1987.362297764816</v>
+        <v>1787.985118582429</v>
       </c>
     </row>
     <row r="43">
@@ -2461,22 +2461,22 @@
         <v>1256.692078957697</v>
       </c>
       <c r="H43">
-        <v>1631.070190145469</v>
+        <v>1389.587765147508</v>
       </c>
       <c r="I43">
-        <v>1111.817105718409</v>
+        <v>948.9976167858401</v>
       </c>
       <c r="J43">
-        <v>2146.171536873176</v>
+        <v>1831.138584181152</v>
       </c>
       <c r="K43">
-        <v>2829.670502491796</v>
+        <v>2587.486973511487</v>
       </c>
       <c r="L43">
-        <v>2303.250182235928</v>
+        <v>2139.871116548657</v>
       </c>
       <c r="M43">
-        <v>3344.331046878731</v>
+        <v>3033.107744226651</v>
       </c>
     </row>
     <row r="44">
@@ -2510,22 +2510,22 @@
         <v>1169.358596830406</v>
       </c>
       <c r="H44">
-        <v>809.5256949007141</v>
+        <v>661.4326691664348</v>
       </c>
       <c r="I44">
-        <v>597.6542145386885</v>
+        <v>488.9916274984137</v>
       </c>
       <c r="J44">
-        <v>1027.280569427886</v>
+        <v>839.4682722556095</v>
       </c>
       <c r="K44">
-        <v>1846.696131736796</v>
+        <v>1699.417923785609</v>
       </c>
       <c r="L44">
-        <v>1594.428670391064</v>
+        <v>1483.075036623749</v>
       </c>
       <c r="M44">
-        <v>2101.82462403074</v>
+        <v>1922.328571924916</v>
       </c>
     </row>
     <row r="45">
@@ -2559,22 +2559,22 @@
         <v>946.8810291892524</v>
       </c>
       <c r="H45">
-        <v>1388.878625225619</v>
+        <v>1140.696575279465</v>
       </c>
       <c r="I45">
-        <v>1023.41421571747</v>
+        <v>845.4101467538458</v>
       </c>
       <c r="J45">
-        <v>1758.994064909491</v>
+        <v>1440.69762715779</v>
       </c>
       <c r="K45">
-        <v>2221.913084868831</v>
+        <v>1970.213980997984</v>
       </c>
       <c r="L45">
-        <v>1836.355151442538</v>
+        <v>1650.952005537873</v>
       </c>
       <c r="M45">
-        <v>2611.826463030303</v>
+        <v>2294.04612071036</v>
       </c>
     </row>
     <row r="46">
@@ -2608,22 +2608,22 @@
         <v>1256.417407733772</v>
       </c>
       <c r="H46">
-        <v>1182.407336962985</v>
+        <v>947.1159024111901</v>
       </c>
       <c r="I46">
-        <v>863.0645912419852</v>
+        <v>690.3798397463748</v>
       </c>
       <c r="J46">
-        <v>1508.519738279838</v>
+        <v>1209.592988714175</v>
       </c>
       <c r="K46">
-        <v>2335.204916813523</v>
+        <v>2100.896316518991</v>
       </c>
       <c r="L46">
-        <v>2003.462198105935</v>
+        <v>1828.934472290222</v>
       </c>
       <c r="M46">
-        <v>2680.469531055724</v>
+        <v>2382.422893990772</v>
       </c>
     </row>
     <row r="47">
@@ -2657,22 +2657,22 @@
         <v>1208.424669086275</v>
       </c>
       <c r="H47">
-        <v>1229.055723898299</v>
+        <v>851.1859671651423</v>
       </c>
       <c r="I47">
-        <v>775.0016100042909</v>
+        <v>555.3083319310625</v>
       </c>
       <c r="J47">
-        <v>1759.894094832912</v>
+        <v>1153.336290778568</v>
       </c>
       <c r="K47">
-        <v>2340.280232070647</v>
+        <v>1962.799092629695</v>
       </c>
       <c r="L47">
-        <v>1866.982037108426</v>
+        <v>1649.450549014576</v>
       </c>
       <c r="M47">
-        <v>2875.642960166675</v>
+        <v>2279.016360330558</v>
       </c>
     </row>
     <row r="48">
@@ -2706,22 +2706,22 @@
         <v>1494.286959261488</v>
       </c>
       <c r="H48">
-        <v>1409.612011075262</v>
+        <v>1139.869947912354</v>
       </c>
       <c r="I48">
-        <v>1023.764058063883</v>
+        <v>829.6388359849408</v>
       </c>
       <c r="J48">
-        <v>1795.359831377984</v>
+        <v>1450.611503392028</v>
       </c>
       <c r="K48">
-        <v>2460.881670506005</v>
+        <v>2190.656283270092</v>
       </c>
       <c r="L48">
-        <v>1871.194619655125</v>
+        <v>1651.870127097819</v>
       </c>
       <c r="M48">
-        <v>3041.357579682707</v>
+        <v>2731.02529130227</v>
       </c>
     </row>
     <row r="49">
@@ -2755,22 +2755,22 @@
         <v>886.9993189402113</v>
       </c>
       <c r="H49">
-        <v>1715.412291438047</v>
+        <v>1202.992614747369</v>
       </c>
       <c r="I49">
-        <v>996.9425219246597</v>
+        <v>742.6482976715979</v>
       </c>
       <c r="J49">
-        <v>2562.526982200895</v>
+        <v>1685.421532981533</v>
       </c>
       <c r="K49">
-        <v>2315.32729928846</v>
+        <v>1801.932737502294</v>
       </c>
       <c r="L49">
-        <v>1548.859753903542</v>
+        <v>1268.508242858589</v>
       </c>
       <c r="M49">
-        <v>3212.115158938748</v>
+        <v>2367.296698025097</v>
       </c>
     </row>
     <row r="50">
@@ -2804,22 +2804,22 @@
         <v>192.6399196192678</v>
       </c>
       <c r="H50">
-        <v>961.3406987026233</v>
+        <v>620.2997197461618</v>
       </c>
       <c r="I50">
-        <v>656.1972585348724</v>
+        <v>422.238279791525</v>
       </c>
       <c r="J50">
-        <v>1269.850533050356</v>
+        <v>818.8017718820059</v>
       </c>
       <c r="K50">
-        <v>1132.719745339802</v>
+        <v>790.9945873500628</v>
       </c>
       <c r="L50">
-        <v>825.3331299494832</v>
+        <v>593.2107378782852</v>
       </c>
       <c r="M50">
-        <v>1442.14492897189</v>
+        <v>990.3803067562724</v>
       </c>
     </row>
     <row r="51">
@@ -2853,22 +2853,22 @@
         <v>215.8398224897602</v>
       </c>
       <c r="H51">
-        <v>1661.492369551324</v>
+        <v>1164.06830269768</v>
       </c>
       <c r="I51">
-        <v>1088.108004273573</v>
+        <v>732.2050891553336</v>
       </c>
       <c r="J51">
-        <v>2261.874896144084</v>
+        <v>1607.72901712716</v>
       </c>
       <c r="K51">
-        <v>1855.10980993157</v>
+        <v>1357.338764322716</v>
       </c>
       <c r="L51">
-        <v>1281.369368055884</v>
+        <v>926.1498404217153</v>
       </c>
       <c r="M51">
-        <v>2458.375571716315</v>
+        <v>1802.559975497453</v>
       </c>
     </row>
     <row r="52">
@@ -2902,22 +2902,22 @@
         <v>454.5971552482208</v>
       </c>
       <c r="H52">
-        <v>1443.2175363908</v>
+        <v>945.5745482657744</v>
       </c>
       <c r="I52">
-        <v>1256.712789294694</v>
+        <v>822.6281974075147</v>
       </c>
       <c r="J52">
-        <v>1633.887069741167</v>
+        <v>1070.708007873476</v>
       </c>
       <c r="K52">
-        <v>1881.855036605858</v>
+        <v>1383.156128527502</v>
       </c>
       <c r="L52">
-        <v>1693.282301427646</v>
+        <v>1259.305394604164</v>
       </c>
       <c r="M52">
-        <v>2072.686084880364</v>
+        <v>1509.600313755052</v>
       </c>
     </row>
     <row r="53">
@@ -2951,22 +2951,22 @@
         <v>500.8304144067867</v>
       </c>
       <c r="H53">
-        <v>1879.232064838198</v>
+        <v>1262.161937678132</v>
       </c>
       <c r="I53">
-        <v>1558.051719552049</v>
+        <v>1030.541542744444</v>
       </c>
       <c r="J53">
-        <v>2202.577651323606</v>
+        <v>1494.395198179606</v>
       </c>
       <c r="K53">
-        <v>2362.565965461967</v>
+        <v>1745.00342457243</v>
       </c>
       <c r="L53">
-        <v>2042.516645170521</v>
+        <v>1513.540709022008</v>
       </c>
       <c r="M53">
-        <v>2685.515505070338</v>
+        <v>1976.546847112002</v>
       </c>
     </row>
     <row r="54">
@@ -3000,22 +3000,22 @@
         <v>873.3325846912594</v>
       </c>
       <c r="H54">
-        <v>1499.724070210581</v>
+        <v>935.3821218441826</v>
       </c>
       <c r="I54">
-        <v>1086.371766987114</v>
+        <v>679.8148198036168</v>
       </c>
       <c r="J54">
-        <v>1909.354627077719</v>
+        <v>1186.271161535378</v>
       </c>
       <c r="K54">
-        <v>2216.551913643914</v>
+        <v>1652.208667042054</v>
       </c>
       <c r="L54">
-        <v>1775.524742376545</v>
+        <v>1355.498588325624</v>
       </c>
       <c r="M54">
-        <v>2664.362364544304</v>
+        <v>1952.504586284168</v>
       </c>
     </row>
     <row r="55">
@@ -3049,22 +3049,22 @@
         <v>966.0514172147025</v>
       </c>
       <c r="H55">
-        <v>1149.705572065578</v>
+        <v>635.062745095447</v>
       </c>
       <c r="I55">
-        <v>745.6676829552433</v>
+        <v>410.7103067750328</v>
       </c>
       <c r="J55">
-        <v>1579.215152840431</v>
+        <v>877.1534030985972</v>
       </c>
       <c r="K55">
-        <v>1954.689534882161</v>
+        <v>1441.335433848899</v>
       </c>
       <c r="L55">
-        <v>1518.456775545264</v>
+        <v>1168.554372116351</v>
       </c>
       <c r="M55">
-        <v>2410.588901488794</v>
+        <v>1726.3494863754</v>
       </c>
     </row>
     <row r="56">
@@ -3098,22 +3098,22 @@
         <v>660.2990270451711</v>
       </c>
       <c r="H56">
-        <v>1262.81558850066</v>
+        <v>813.3857790442489</v>
       </c>
       <c r="I56">
-        <v>1004.765526665153</v>
+        <v>649.6750415661014</v>
       </c>
       <c r="J56">
-        <v>1523.454742747864</v>
+        <v>980.4722066401471</v>
       </c>
       <c r="K56">
-        <v>1880.23381946451</v>
+        <v>1430.419203038405</v>
       </c>
       <c r="L56">
-        <v>1618.08718554658</v>
+        <v>1260.750791431799</v>
       </c>
       <c r="M56">
-        <v>2143.763218289456</v>
+        <v>1601.880846579361</v>
       </c>
     </row>
     <row r="57">
@@ -3147,22 +3147,22 @@
         <v>766.218553642918</v>
       </c>
       <c r="H57">
-        <v>1736.3879961107</v>
+        <v>1189.973035496994</v>
       </c>
       <c r="I57">
-        <v>1271.657363869838</v>
+        <v>836.8919962811293</v>
       </c>
       <c r="J57">
-        <v>2205.989624914656</v>
+        <v>1536.084935618748</v>
       </c>
       <c r="K57">
-        <v>2455.0285953046</v>
+        <v>1909.39726533061</v>
       </c>
       <c r="L57">
-        <v>1990.776762763972</v>
+        <v>1555.43044566034</v>
       </c>
       <c r="M57">
-        <v>2928.501929447704</v>
+        <v>2260.720784750149</v>
       </c>
     </row>
     <row r="58">
@@ -3196,22 +3196,22 @@
         <v>978.8352203260482</v>
       </c>
       <c r="H58">
-        <v>1681.949672978886</v>
+        <v>1060.963207460515</v>
       </c>
       <c r="I58">
-        <v>1225.223713699896</v>
+        <v>775.8509503926492</v>
       </c>
       <c r="J58">
-        <v>2136.155755516653</v>
+        <v>1344.017191504646</v>
       </c>
       <c r="K58">
-        <v>2556.279160658931</v>
+        <v>1935.949652550131</v>
       </c>
       <c r="L58">
-        <v>2084.146783537861</v>
+        <v>1628.844320693424</v>
       </c>
       <c r="M58">
-        <v>3024.703043349924</v>
+        <v>2239.277880382867</v>
       </c>
     </row>
     <row r="59">
@@ -3245,22 +3245,22 @@
         <v>801.618623278103</v>
       </c>
       <c r="H59">
-        <v>1100.978417690927</v>
+        <v>737.7765284237321</v>
       </c>
       <c r="I59">
-        <v>651.4559293306513</v>
+        <v>400.3278150405973</v>
       </c>
       <c r="J59">
-        <v>1558.949210409336</v>
+        <v>1090.69833806895</v>
       </c>
       <c r="K59">
-        <v>1809.457508603199</v>
+        <v>1447.925738107096</v>
       </c>
       <c r="L59">
-        <v>1345.453234195418</v>
+        <v>1099.827473687042</v>
       </c>
       <c r="M59">
-        <v>2278.587438140087</v>
+        <v>1808.261470111791</v>
       </c>
     </row>
     <row r="60">
@@ -3294,22 +3294,22 @@
         <v>1147.010594844196</v>
       </c>
       <c r="H60">
-        <v>1339.002738843035</v>
+        <v>847.8742818598222</v>
       </c>
       <c r="I60">
-        <v>952.9933889454356</v>
+        <v>607.3533383674653</v>
       </c>
       <c r="J60">
-        <v>1727.02743901001</v>
+        <v>1090.927371150548</v>
       </c>
       <c r="K60">
-        <v>2368.462889151155</v>
+        <v>1876.864783826629</v>
       </c>
       <c r="L60">
-        <v>1964.476298567159</v>
+        <v>1610.833710717948</v>
       </c>
       <c r="M60">
-        <v>2771.875121338308</v>
+        <v>2147.271876666281</v>
       </c>
     </row>
     <row r="61">
@@ -3343,22 +3343,22 @@
         <v>948.3386585721115</v>
       </c>
       <c r="H61">
-        <v>1483.093796229438</v>
+        <v>1037.114197477657</v>
       </c>
       <c r="I61">
-        <v>971.1044259728757</v>
+        <v>656.6842916236675</v>
       </c>
       <c r="J61">
-        <v>1989.666084546172</v>
+        <v>1420.833317097377</v>
       </c>
       <c r="K61">
-        <v>2326.012901575324</v>
+        <v>1880.508658175986</v>
       </c>
       <c r="L61">
-        <v>1806.40957374193</v>
+        <v>1493.245017451885</v>
       </c>
       <c r="M61">
-        <v>2847.606746615643</v>
+        <v>2279.621012967795</v>
       </c>
     </row>
     <row r="62">
@@ -3392,22 +3392,22 @@
         <v>711.3279070822051</v>
       </c>
       <c r="H62">
-        <v>1296.190260193649</v>
+        <v>834.7512253850996</v>
       </c>
       <c r="I62">
-        <v>961.2362446613837</v>
+        <v>618.2467575972561</v>
       </c>
       <c r="J62">
-        <v>1629.380708259931</v>
+        <v>1050.452025315686</v>
       </c>
       <c r="K62">
-        <v>1888.319221558585</v>
+        <v>1425.101261423737</v>
       </c>
       <c r="L62">
-        <v>1531.466172819924</v>
+        <v>1175.223031247653</v>
       </c>
       <c r="M62">
-        <v>2242.27187059024</v>
+        <v>1669.509451425063</v>
       </c>
     </row>
     <row r="63">
@@ -3441,22 +3441,22 @@
         <v>761.4122106825737</v>
       </c>
       <c r="H63">
-        <v>2281.794910028154</v>
+        <v>1649.592132550313</v>
       </c>
       <c r="I63">
-        <v>1538.33582026837</v>
+        <v>1037.378736207171</v>
       </c>
       <c r="J63">
-        <v>3031.402626531468</v>
+        <v>2266.376080284439</v>
       </c>
       <c r="K63">
-        <v>2926.043288469386</v>
+        <v>2293.296315796785</v>
       </c>
       <c r="L63">
-        <v>2177.09419943167</v>
+        <v>1673.071753506542</v>
       </c>
       <c r="M63">
-        <v>3688.443996351666</v>
+        <v>2920.44265821342</v>
       </c>
     </row>
     <row r="64">
@@ -3490,22 +3490,22 @@
         <v>652.3322601827206</v>
       </c>
       <c r="H64">
-        <v>1386.157558890133</v>
+        <v>901.1767321523313</v>
       </c>
       <c r="I64">
-        <v>1025.219658781008</v>
+        <v>667.0816248337437</v>
       </c>
       <c r="J64">
-        <v>1756.121250208094</v>
+        <v>1137.429126275036</v>
       </c>
       <c r="K64">
-        <v>1969.664321316808</v>
+        <v>1484.437433299224</v>
       </c>
       <c r="L64">
-        <v>1600.478446638591</v>
+        <v>1241.992968465407</v>
       </c>
       <c r="M64">
-        <v>2348.162523617601</v>
+        <v>1735.22346000023</v>
       </c>
     </row>
     <row r="65">
@@ -3539,22 +3539,22 @@
         <v>646.2002545975834</v>
       </c>
       <c r="H65">
-        <v>1443.783585879391</v>
+        <v>915.5252414856607</v>
       </c>
       <c r="I65">
-        <v>997.2289125502593</v>
+        <v>611.3496069417573</v>
       </c>
       <c r="J65">
-        <v>1916.368861978772</v>
+        <v>1236.2228874396</v>
       </c>
       <c r="K65">
-        <v>2022.643897388225</v>
+        <v>1491.642959889037</v>
       </c>
       <c r="L65">
-        <v>1567.093487547547</v>
+        <v>1182.004191755941</v>
       </c>
       <c r="M65">
-        <v>2497.771969006837</v>
+        <v>1823.196017626387</v>
       </c>
     </row>
     <row r="66">
@@ -3588,22 +3588,22 @@
         <v>2057.885464261902</v>
       </c>
       <c r="H66">
-        <v>1341.14017787382</v>
+        <v>854.1414442274236</v>
       </c>
       <c r="I66">
-        <v>991.4692147214236</v>
+        <v>636.7110773795351</v>
       </c>
       <c r="J66">
-        <v>1694.756398044293</v>
+        <v>1075.352589838953</v>
       </c>
       <c r="K66">
-        <v>3168.178172646825</v>
+        <v>2682.032696020567</v>
       </c>
       <c r="L66">
-        <v>2749.69478932442</v>
+        <v>2365.864581092727</v>
       </c>
       <c r="M66">
-        <v>3595.582811715429</v>
+        <v>3002.410351759164</v>
       </c>
     </row>
     <row r="67">
@@ -3637,22 +3637,22 @@
         <v>1312.239832941063</v>
       </c>
       <c r="H67">
-        <v>778.3807754159551</v>
+        <v>469.7245836116142</v>
       </c>
       <c r="I67">
-        <v>454.97229548313</v>
+        <v>270.320953844666</v>
       </c>
       <c r="J67">
-        <v>1134.332677030444</v>
+        <v>692.5648673126735</v>
       </c>
       <c r="K67">
-        <v>1926.352832969776</v>
+        <v>1619.208522633521</v>
       </c>
       <c r="L67">
-        <v>1560.74026683069</v>
+        <v>1357.791535775816</v>
       </c>
       <c r="M67">
-        <v>2323.578469077275</v>
+        <v>1899.981916265082</v>
       </c>
     </row>
     <row r="68">
@@ -3686,22 +3686,22 @@
         <v>702.857800477555</v>
       </c>
       <c r="H68">
-        <v>1664.183684267527</v>
+        <v>1051.97394274739</v>
       </c>
       <c r="I68">
-        <v>1188.983593119645</v>
+        <v>758.7183278840354</v>
       </c>
       <c r="J68">
-        <v>2142.981914421067</v>
+        <v>1348.91590783112</v>
       </c>
       <c r="K68">
-        <v>2259.827448314483</v>
+        <v>1646.528339767933</v>
       </c>
       <c r="L68">
-        <v>1779.01970151086</v>
+        <v>1339.527093370337</v>
       </c>
       <c r="M68">
-        <v>2751.678898780138</v>
+        <v>1965.511857871011</v>
       </c>
     </row>
     <row r="69">
@@ -3735,22 +3735,22 @@
         <v>886.2568702286067</v>
       </c>
       <c r="H69">
-        <v>1841.037517761517</v>
+        <v>1201.122492284986</v>
       </c>
       <c r="I69">
-        <v>1248.673699704486</v>
+        <v>778.0671220722194</v>
       </c>
       <c r="J69">
-        <v>2469.579864747195</v>
+        <v>1653.437842009879</v>
       </c>
       <c r="K69">
-        <v>2606.884308032223</v>
+        <v>1963.420212411965</v>
       </c>
       <c r="L69">
-        <v>1998.048881509514</v>
+        <v>1529.208107756471</v>
       </c>
       <c r="M69">
-        <v>3239.87591476537</v>
+        <v>2433.759378738558</v>
       </c>
     </row>
     <row r="70">
@@ -3784,22 +3784,22 @@
         <v>441.6843504881658</v>
       </c>
       <c r="H70">
-        <v>1388.587818366545</v>
+        <v>897.2363503806885</v>
       </c>
       <c r="I70">
-        <v>1061.488828575222</v>
+        <v>685.7465215581452</v>
       </c>
       <c r="J70">
-        <v>1731.40529282488</v>
+        <v>1115.085014752152</v>
       </c>
       <c r="K70">
-        <v>1731.343424642953</v>
+        <v>1239.36201922473</v>
       </c>
       <c r="L70">
-        <v>1385.691050180592</v>
+        <v>1000.18413788307</v>
       </c>
       <c r="M70">
-        <v>2084.404211318089</v>
+        <v>1476.117526007631</v>
       </c>
     </row>
     <row r="71">
@@ -3833,22 +3833,22 @@
         <v>508.5902987194033</v>
       </c>
       <c r="H71">
-        <v>1351.711841295989</v>
+        <v>904.0456618202228</v>
       </c>
       <c r="I71">
-        <v>881.2385383421586</v>
+        <v>571.2173445265587</v>
       </c>
       <c r="J71">
-        <v>1864.79900573352</v>
+        <v>1282.027542083165</v>
       </c>
       <c r="K71">
-        <v>1756.913287198129</v>
+        <v>1310.301664292862</v>
       </c>
       <c r="L71">
-        <v>1276.785282613202</v>
+        <v>960.4808233265938</v>
       </c>
       <c r="M71">
-        <v>2276.86298455841</v>
+        <v>1694.601510804225</v>
       </c>
     </row>
     <row r="72">
@@ -3882,22 +3882,22 @@
         <v>865.134688224887</v>
       </c>
       <c r="H72">
-        <v>1774.58294492603</v>
+        <v>1118.715805126683</v>
       </c>
       <c r="I72">
-        <v>1337.321359789988</v>
+        <v>844.2873538851118</v>
       </c>
       <c r="J72">
-        <v>2212.827942698265</v>
+        <v>1394.931680628285</v>
       </c>
       <c r="K72">
-        <v>2466.137501870786</v>
+        <v>1809.761953898054</v>
       </c>
       <c r="L72">
-        <v>1988.581540861994</v>
+        <v>1480.722697861272</v>
       </c>
       <c r="M72">
-        <v>2939.223109942141</v>
+        <v>2139.635896256736</v>
       </c>
     </row>
     <row r="73">
@@ -3931,22 +3931,22 @@
         <v>994.4138228116267</v>
       </c>
       <c r="H73">
-        <v>1797.34818492224</v>
+        <v>1145.787114089835</v>
       </c>
       <c r="I73">
-        <v>1252.140121408344</v>
+        <v>753.5723339878278</v>
       </c>
       <c r="J73">
-        <v>2361.057536411831</v>
+        <v>1548.878862699323</v>
       </c>
       <c r="K73">
-        <v>2610.741364899912</v>
+        <v>1958.062928807021</v>
       </c>
       <c r="L73">
-        <v>2020.994738132872</v>
+        <v>1516.887554538307</v>
       </c>
       <c r="M73">
-        <v>3215.92080779868</v>
+        <v>2412.663251418605</v>
       </c>
     </row>
     <row r="74">
@@ -3980,22 +3980,22 @@
         <v>1229.827409899085</v>
       </c>
       <c r="H74">
-        <v>1101.776536302894</v>
+        <v>701.0455008772001</v>
       </c>
       <c r="I74">
-        <v>802.6292006817432</v>
+        <v>513.6496913376035</v>
       </c>
       <c r="J74">
-        <v>1399.3971914124</v>
+        <v>887.320954161945</v>
       </c>
       <c r="K74">
-        <v>2247.140728193976</v>
+        <v>1847.753926344976</v>
       </c>
       <c r="L74">
-        <v>1938.52075365656</v>
+        <v>1642.636485182096</v>
       </c>
       <c r="M74">
-        <v>2559.446862316547</v>
+        <v>2053.216465828314</v>
       </c>
     </row>
     <row r="75">
@@ -4029,22 +4029,22 @@
         <v>1388.502376612042</v>
       </c>
       <c r="H75">
-        <v>1568.732368764568</v>
+        <v>1052.283822876057</v>
       </c>
       <c r="I75">
-        <v>1042.898941399817</v>
+        <v>675.1320178263871</v>
       </c>
       <c r="J75">
-        <v>2118.907864657962</v>
+        <v>1440.856662910082</v>
       </c>
       <c r="K75">
-        <v>2867.880339388785</v>
+        <v>2350.871436093634</v>
       </c>
       <c r="L75">
-        <v>2329.780101377575</v>
+        <v>1961.604144043576</v>
       </c>
       <c r="M75">
-        <v>3429.199637623633</v>
+        <v>2750.933184651958</v>
       </c>
     </row>
     <row r="76">
@@ -4078,22 +4078,22 @@
         <v>1362.502229211572</v>
       </c>
       <c r="H76">
-        <v>970.1980941318207</v>
+        <v>656.2775856558869</v>
       </c>
       <c r="I76">
-        <v>658.5639684392603</v>
+        <v>449.9259880450405</v>
       </c>
       <c r="J76">
-        <v>1314.592383105733</v>
+        <v>882.8097890052496</v>
       </c>
       <c r="K76">
-        <v>2201.071225661688</v>
+        <v>1885.788475085308</v>
       </c>
       <c r="L76">
-        <v>1854.010072060061</v>
+        <v>1635.537255543242</v>
       </c>
       <c r="M76">
-        <v>2569.247131113118</v>
+        <v>2148.265201706998</v>
       </c>
     </row>
     <row r="77">
@@ -4127,22 +4127,22 @@
         <v>1105.702359464523</v>
       </c>
       <c r="H77">
-        <v>1151.371530628396</v>
+        <v>795.9165395251649</v>
       </c>
       <c r="I77">
-        <v>686.9011556431993</v>
+        <v>450.5888751137601</v>
       </c>
       <c r="J77">
-        <v>1654.335818487701</v>
+        <v>1165.154080868079</v>
       </c>
       <c r="K77">
-        <v>2148.160660512876</v>
+        <v>1787.930090855084</v>
       </c>
       <c r="L77">
-        <v>1671.967615650722</v>
+        <v>1433.503486780009</v>
       </c>
       <c r="M77">
-        <v>2663.065006132813</v>
+        <v>2172.660139817603</v>
       </c>
     </row>
     <row r="78">
@@ -4176,22 +4176,22 @@
         <v>1547.296751245271</v>
       </c>
       <c r="H78">
-        <v>1172.224968907885</v>
+        <v>766.9488176797704</v>
       </c>
       <c r="I78">
-        <v>799.0142577308224</v>
+        <v>523.7429713011214</v>
       </c>
       <c r="J78">
-        <v>1544.686000561808</v>
+        <v>1007.838343681142</v>
       </c>
       <c r="K78">
-        <v>2537.564178768474</v>
+        <v>2131.733395841246</v>
       </c>
       <c r="L78">
-        <v>2122.774243167505</v>
+        <v>1830.998246360804</v>
       </c>
       <c r="M78">
-        <v>2957.274547819501</v>
+        <v>2433.411954790045</v>
       </c>
     </row>
     <row r="79">
@@ -4225,22 +4225,22 @@
         <v>1415.7077162407</v>
       </c>
       <c r="H79">
-        <v>1399.547358212801</v>
+        <v>925.5733158888156</v>
       </c>
       <c r="I79">
-        <v>840.6175991481235</v>
+        <v>508.3348643864578</v>
       </c>
       <c r="J79">
-        <v>2008.089876600627</v>
+        <v>1391.839406744863</v>
       </c>
       <c r="K79">
-        <v>2647.235595415585</v>
+        <v>2173.189265640206</v>
       </c>
       <c r="L79">
-        <v>2067.994716284885</v>
+        <v>1734.574789278355</v>
       </c>
       <c r="M79">
-        <v>3268.276868168809</v>
+        <v>2659.982356449743</v>
       </c>
     </row>
     <row r="80">
@@ -4274,22 +4274,22 @@
         <v>660.3656559805313</v>
       </c>
       <c r="H80">
-        <v>1268.350711278547</v>
+        <v>812.850773617783</v>
       </c>
       <c r="I80">
-        <v>928.6802620028251</v>
+        <v>599.4494274194783</v>
       </c>
       <c r="J80">
-        <v>1613.761093887024</v>
+        <v>1030.402645655229</v>
       </c>
       <c r="K80">
-        <v>1831.296507766232</v>
+        <v>1375.55940284552</v>
       </c>
       <c r="L80">
-        <v>1475.139101272341</v>
+        <v>1140.114668880345</v>
       </c>
       <c r="M80">
-        <v>2188.565420166996</v>
+        <v>1616.066017471962</v>
       </c>
     </row>
     <row r="81">
@@ -4323,22 +4323,22 @@
         <v>667.1604862580762</v>
       </c>
       <c r="H81">
-        <v>2059.018456178317</v>
+        <v>1458.42966099591</v>
       </c>
       <c r="I81">
-        <v>1462.215117467668</v>
+        <v>999.770770860478</v>
       </c>
       <c r="J81">
-        <v>2693.185505919144</v>
+        <v>1943.801557660582</v>
       </c>
       <c r="K81">
-        <v>2631.391480376958</v>
+        <v>2031.411011349796</v>
       </c>
       <c r="L81">
-        <v>2029.445551688005</v>
+        <v>1567.706816991184</v>
       </c>
       <c r="M81">
-        <v>3264.551173158816</v>
+        <v>2522.512351009108</v>
       </c>
     </row>
     <row r="82">
@@ -4372,22 +4372,22 @@
         <v>1061.984455369622</v>
       </c>
       <c r="H82">
-        <v>1176.812112249017</v>
+        <v>753.9857691726504</v>
       </c>
       <c r="I82">
-        <v>843.6294215967215</v>
+        <v>542.5255533189813</v>
       </c>
       <c r="J82">
-        <v>1515.426723979243</v>
+        <v>967.572232078783</v>
       </c>
       <c r="K82">
-        <v>2132.004618649664</v>
+        <v>1710.063484510286</v>
       </c>
       <c r="L82">
-        <v>1784.760497965743</v>
+        <v>1477.248741315037</v>
       </c>
       <c r="M82">
-        <v>2488.884284101285</v>
+        <v>1948.350789692081</v>
       </c>
     </row>
     <row r="83">
@@ -4421,22 +4421,22 @@
         <v>888.8778958358703</v>
       </c>
       <c r="H83">
-        <v>1821.230213168814</v>
+        <v>1171.782774310704</v>
       </c>
       <c r="I83">
-        <v>1182.925395002914</v>
+        <v>736.7629237142804</v>
       </c>
       <c r="J83">
-        <v>2511.648482681282</v>
+        <v>1656.857603328923</v>
       </c>
       <c r="K83">
-        <v>2613.596592154322</v>
+        <v>1966.048637062602</v>
       </c>
       <c r="L83">
-        <v>1972.427084976621</v>
+        <v>1520.830990595801</v>
       </c>
       <c r="M83">
-        <v>3310.997170905402</v>
+        <v>2456.720537628532</v>
       </c>
     </row>
     <row r="84">
@@ -4470,22 +4470,22 @@
         <v>1792.689493915799</v>
       </c>
       <c r="H84">
-        <v>1751.345045890051</v>
+        <v>1115.190821046036</v>
       </c>
       <c r="I84">
-        <v>1306.7021270196</v>
+        <v>834.971477885879</v>
       </c>
       <c r="J84">
-        <v>2199.498477497434</v>
+        <v>1396.010800613615</v>
       </c>
       <c r="K84">
-        <v>3381.050065388795</v>
+        <v>2743.147817575007</v>
       </c>
       <c r="L84">
-        <v>2902.190606005871</v>
+        <v>2416.77312596588</v>
       </c>
       <c r="M84">
-        <v>3856.798433560296</v>
+        <v>3071.44026041102</v>
       </c>
     </row>
     <row r="85">
@@ -4519,22 +4519,22 @@
         <v>1604.325719362528</v>
       </c>
       <c r="H85">
-        <v>2269.577940556572</v>
+        <v>1551.951527769711</v>
       </c>
       <c r="I85">
-        <v>1541.475994068675</v>
+        <v>1026.156965371871</v>
       </c>
       <c r="J85">
-        <v>3010.152135868987</v>
+        <v>2080.572951260983</v>
       </c>
       <c r="K85">
-        <v>3728.987983410598</v>
+        <v>3009.880793914236</v>
       </c>
       <c r="L85">
-        <v>2984.922515943832</v>
+        <v>2465.627182589622</v>
       </c>
       <c r="M85">
-        <v>4483.645899903688</v>
+        <v>3553.303450027101</v>
       </c>
     </row>
     <row r="86">
@@ -4568,22 +4568,22 @@
         <v>1216.468889513729</v>
       </c>
       <c r="H86">
-        <v>1547.845069312499</v>
+        <v>1002.674227809774</v>
       </c>
       <c r="I86">
-        <v>1142.799065812753</v>
+        <v>745.3499335778074</v>
       </c>
       <c r="J86">
-        <v>1944.972977953996</v>
+        <v>1256.065854166012</v>
       </c>
       <c r="K86">
-        <v>2603.246608642551</v>
+        <v>2058.9023348323</v>
       </c>
       <c r="L86">
-        <v>2170.328329164943</v>
+        <v>1752.359587371008</v>
       </c>
       <c r="M86">
-        <v>3029.50976886091</v>
+        <v>2358.492287161701</v>
       </c>
     </row>
     <row r="87">
@@ -4617,22 +4617,22 @@
         <v>1252.129300065167</v>
       </c>
       <c r="H87">
-        <v>1608.730141234589</v>
+        <v>1087.020813523262</v>
       </c>
       <c r="I87">
-        <v>1063.409446193111</v>
+        <v>674.5566608039101</v>
       </c>
       <c r="J87">
-        <v>2152.54125404859</v>
+        <v>1498.493648083588</v>
       </c>
       <c r="K87">
-        <v>2697.96977210449</v>
+        <v>2174.665759599198</v>
       </c>
       <c r="L87">
-        <v>2121.930344376794</v>
+        <v>1720.960923666066</v>
       </c>
       <c r="M87">
-        <v>3273.900679122839</v>
+        <v>2620.188935878009</v>
       </c>
     </row>
     <row r="88">
@@ -4666,22 +4666,22 @@
         <v>975.123693400439</v>
       </c>
       <c r="H88">
-        <v>1740.946963703689</v>
+        <v>1112.237083833757</v>
       </c>
       <c r="I88">
-        <v>1277.797498416989</v>
+        <v>821.3931562570749</v>
       </c>
       <c r="J88">
-        <v>2206.264093198844</v>
+        <v>1408.895951844695</v>
       </c>
       <c r="K88">
-        <v>2495.948649553731</v>
+        <v>1869.554622904868</v>
       </c>
       <c r="L88">
-        <v>1986.543674197243</v>
+        <v>1505.523779743842</v>
       </c>
       <c r="M88">
-        <v>3022.912159068331</v>
+        <v>2239.50418810771</v>
       </c>
     </row>
     <row r="89">
@@ -4715,22 +4715,22 @@
         <v>1100.890456859378</v>
       </c>
       <c r="H89">
-        <v>1736.563316689971</v>
+        <v>1222.319815805228</v>
       </c>
       <c r="I89">
-        <v>1137.815117812077</v>
+        <v>763.922008946828</v>
       </c>
       <c r="J89">
-        <v>2323.702716870206</v>
+        <v>1666.357314742153</v>
       </c>
       <c r="K89">
-        <v>2628.417254450574</v>
+        <v>2107.918471060885</v>
       </c>
       <c r="L89">
-        <v>1992.912705657107</v>
+        <v>1605.684591661248</v>
       </c>
       <c r="M89">
-        <v>3258.304172258919</v>
+        <v>2612.113378834341</v>
       </c>
     </row>
     <row r="90">
@@ -4764,22 +4764,22 @@
         <v>700.3836393078114</v>
       </c>
       <c r="H90">
-        <v>906.294269790198</v>
+        <v>576.3271458192709</v>
       </c>
       <c r="I90">
-        <v>696.5968680434536</v>
+        <v>444.2493440322601</v>
       </c>
       <c r="J90">
-        <v>1116.580524751799</v>
+        <v>707.2203844459546</v>
       </c>
       <c r="K90">
-        <v>1561.072754241382</v>
+        <v>1231.680676254583</v>
       </c>
       <c r="L90">
-        <v>1348.276265634946</v>
+        <v>1093.386930697624</v>
       </c>
       <c r="M90">
-        <v>1774.376495134797</v>
+        <v>1370.293176435181</v>
       </c>
     </row>
     <row r="91">
@@ -4813,22 +4813,22 @@
         <v>780.9152618808932</v>
       </c>
       <c r="H91">
-        <v>1788.344405538319</v>
+        <v>1222.980404044597</v>
       </c>
       <c r="I91">
-        <v>1327.596050446715</v>
+        <v>881.7577241780874</v>
       </c>
       <c r="J91">
-        <v>2254.861953612389</v>
+        <v>1575.507439986687</v>
       </c>
       <c r="K91">
-        <v>2520.044656703129</v>
+        <v>1956.554627191721</v>
       </c>
       <c r="L91">
-        <v>2061.545092339276</v>
+        <v>1612.944228801993</v>
       </c>
       <c r="M91">
-        <v>2992.246419204873</v>
+        <v>2309.91344077006</v>
       </c>
     </row>
     <row r="92">
@@ -4862,22 +4862,22 @@
         <v>750.4919162185248</v>
       </c>
       <c r="H92">
-        <v>1508.066858141972</v>
+        <v>991.3098583505148</v>
       </c>
       <c r="I92">
-        <v>1113.290525521064</v>
+        <v>740.1925564872773</v>
       </c>
       <c r="J92">
-        <v>1904.48739385222</v>
+        <v>1240.973432607505</v>
       </c>
       <c r="K92">
-        <v>2153.430607655642</v>
+        <v>1635.355944870581</v>
       </c>
       <c r="L92">
-        <v>1748.209084976296</v>
+        <v>1366.567702558989</v>
       </c>
       <c r="M92">
-        <v>2566.474741827569</v>
+        <v>1911.087584262921</v>
       </c>
     </row>
     <row r="93">
@@ -4911,22 +4911,22 @@
         <v>776.2801458497694</v>
       </c>
       <c r="H93">
-        <v>1732.624670010355</v>
+        <v>1104.97752480286</v>
       </c>
       <c r="I93">
-        <v>1159.090502975508</v>
+        <v>691.303521368431</v>
       </c>
       <c r="J93">
-        <v>2336.524003358993</v>
+        <v>1540.035924951829</v>
       </c>
       <c r="K93">
-        <v>2406.155615427717</v>
+        <v>1778.124018544653</v>
       </c>
       <c r="L93">
-        <v>1826.327129654658</v>
+        <v>1357.376773588724</v>
       </c>
       <c r="M93">
-        <v>3015.110045396677</v>
+        <v>2222.904462643246</v>
       </c>
     </row>
     <row r="94">
@@ -4960,22 +4960,22 @@
         <v>1069.430689053872</v>
       </c>
       <c r="H94">
-        <v>1297.05936230303</v>
+        <v>837.6773980682181</v>
       </c>
       <c r="I94">
-        <v>951.3069648293571</v>
+        <v>620.1633892827887</v>
       </c>
       <c r="J94">
-        <v>1651.46365932983</v>
+        <v>1062.208417394191</v>
       </c>
       <c r="K94">
-        <v>2274.317092296295</v>
+        <v>1815.818703075798</v>
       </c>
       <c r="L94">
-        <v>1916.445468490642</v>
+        <v>1576.773149053184</v>
       </c>
       <c r="M94">
-        <v>2641.308455995832</v>
+        <v>2054.92077356453</v>
       </c>
     </row>
     <row r="95">
@@ -5009,22 +5009,22 @@
         <v>1047.808415374264</v>
       </c>
       <c r="H95">
-        <v>1373.212175652262</v>
+        <v>854.3573099013612</v>
       </c>
       <c r="I95">
-        <v>865.1523733248271</v>
+        <v>521.8046144049334</v>
       </c>
       <c r="J95">
-        <v>1927.518713764174</v>
+        <v>1239.091962732432</v>
       </c>
       <c r="K95">
-        <v>2332.953836826606</v>
+        <v>1813.811235514338</v>
       </c>
       <c r="L95">
-        <v>1822.6656633798</v>
+        <v>1471.412215501889</v>
       </c>
       <c r="M95">
-        <v>2895.488325626865</v>
+        <v>2204.328335931337</v>
       </c>
     </row>
     <row r="96">
@@ -5058,22 +5058,22 @@
         <v>987.3884316847525</v>
       </c>
       <c r="H96">
-        <v>1819.164784868681</v>
+        <v>1183.603538703646</v>
       </c>
       <c r="I96">
-        <v>1192.101839741361</v>
+        <v>791.1008696293421</v>
       </c>
       <c r="J96">
-        <v>2522.670531047537</v>
+        <v>1626.091175171689</v>
       </c>
       <c r="K96">
-        <v>2479.526289253922</v>
+        <v>1846.39678495124</v>
       </c>
       <c r="L96">
-        <v>1781.946331555098</v>
+        <v>1340.65451696241</v>
       </c>
       <c r="M96">
-        <v>3247.393987268026</v>
+        <v>2393.117604348666</v>
       </c>
     </row>
     <row r="97">
@@ -5107,22 +5107,22 @@
         <v>1057.392334947969</v>
       </c>
       <c r="H97">
-        <v>2780.429994905984</v>
+        <v>1741.839288230535</v>
       </c>
       <c r="I97">
-        <v>1729.297449349283</v>
+        <v>1047.492412979141</v>
       </c>
       <c r="J97">
-        <v>3851.567285805362</v>
+        <v>2467.986442355834</v>
       </c>
       <c r="K97">
-        <v>3526.907580360471</v>
+        <v>2481.635376194677</v>
       </c>
       <c r="L97">
-        <v>2422.165913739555</v>
+        <v>1714.649181578327</v>
       </c>
       <c r="M97">
-        <v>4629.92840314691</v>
+        <v>3261.415232461618</v>
       </c>
     </row>
     <row r="98">
@@ -5156,22 +5156,22 @@
         <v>209.3351296662951</v>
       </c>
       <c r="H98">
-        <v>1034.73707764542</v>
+        <v>1130.37146923313</v>
       </c>
       <c r="I98">
-        <v>627.4113363513093</v>
+        <v>678.0569897637879</v>
       </c>
       <c r="J98">
-        <v>1448.075627970922</v>
+        <v>1588.289900183286</v>
       </c>
       <c r="K98">
-        <v>1222.021305693626</v>
+        <v>1317.528591343019</v>
       </c>
       <c r="L98">
-        <v>816.556150902322</v>
+        <v>865.0310358737779</v>
       </c>
       <c r="M98">
-        <v>1634.945662766465</v>
+        <v>1772.892376896463</v>
       </c>
     </row>
     <row r="99">
@@ -5205,22 +5205,22 @@
         <v>330.396073732945</v>
       </c>
       <c r="H99">
-        <v>1884.295609458493</v>
+        <v>2019.933996024013</v>
       </c>
       <c r="I99">
-        <v>1137.244419548129</v>
+        <v>1232.011596200835</v>
       </c>
       <c r="J99">
-        <v>2659.969418693005</v>
+        <v>2840.676413893465</v>
       </c>
       <c r="K99">
-        <v>2184.260624340403</v>
+        <v>2317.404570761555</v>
       </c>
       <c r="L99">
-        <v>1428.785479271837</v>
+        <v>1529.638961640164</v>
       </c>
       <c r="M99">
-        <v>2954.379812225606</v>
+        <v>3141.743740116965</v>
       </c>
     </row>
     <row r="100">
@@ -5254,22 +5254,22 @@
         <v>429.208463908387</v>
       </c>
       <c r="H100">
-        <v>1327.660055361164</v>
+        <v>1354.462247923741</v>
       </c>
       <c r="I100">
-        <v>1088.272594590241</v>
+        <v>1097.263639306996</v>
       </c>
       <c r="J100">
-        <v>1563.176992462348</v>
+        <v>1599.319839342707</v>
       </c>
       <c r="K100">
-        <v>1741.761952792422</v>
+        <v>1767.714100157751</v>
       </c>
       <c r="L100">
-        <v>1502.206082298093</v>
+        <v>1509.560947566697</v>
       </c>
       <c r="M100">
-        <v>1976.098537289486</v>
+        <v>2015.477835923144</v>
       </c>
     </row>
     <row r="101">
@@ -5303,22 +5303,22 @@
         <v>485.9127124077401</v>
       </c>
       <c r="H101">
-        <v>1624.021067013651</v>
+        <v>1781.283363316355</v>
       </c>
       <c r="I101">
-        <v>1307.391864265248</v>
+        <v>1428.575940358544</v>
       </c>
       <c r="J101">
-        <v>1935.974006617491</v>
+        <v>2129.708729706746</v>
       </c>
       <c r="K101">
-        <v>2093.64745582535</v>
+        <v>2249.272322531754</v>
       </c>
       <c r="L101">
-        <v>1774.291342510929</v>
+        <v>1894.675448765143</v>
       </c>
       <c r="M101">
-        <v>2407.140243462979</v>
+        <v>2599.159909424519</v>
       </c>
     </row>
     <row r="102">
@@ -5352,22 +5352,22 @@
         <v>767.0233956444729</v>
       </c>
       <c r="H102">
-        <v>1243.932738333223</v>
+        <v>1281.201835741563</v>
       </c>
       <c r="I102">
-        <v>847.7425865621856</v>
+        <v>861.781312851434</v>
       </c>
       <c r="J102">
-        <v>1659.799471801503</v>
+        <v>1720.208067296432</v>
       </c>
       <c r="K102">
-        <v>1869.388880519535</v>
+        <v>1906.45398665242</v>
       </c>
       <c r="L102">
-        <v>1453.17495581559</v>
+        <v>1466.709311057534</v>
       </c>
       <c r="M102">
-        <v>2304.081575551163</v>
+        <v>2367.025991969595</v>
       </c>
     </row>
     <row r="103">
@@ -5401,22 +5401,22 @@
         <v>828.9253659057686</v>
       </c>
       <c r="H103">
-        <v>1647.743986287778</v>
+        <v>1819.443612059116</v>
       </c>
       <c r="I103">
-        <v>1012.625089804366</v>
+        <v>1130.694239494237</v>
       </c>
       <c r="J103">
-        <v>2308.099669411779</v>
+        <v>2536.43480268913</v>
       </c>
       <c r="K103">
-        <v>2332.256096036359</v>
+        <v>2503.942883941663</v>
       </c>
       <c r="L103">
-        <v>1685.386152618074</v>
+        <v>1795.875315314037</v>
       </c>
       <c r="M103">
-        <v>3013.336346347925</v>
+        <v>3251.804691304765</v>
       </c>
     </row>
     <row r="104">
@@ -5450,22 +5450,22 @@
         <v>494.7252323408197</v>
       </c>
       <c r="H104">
-        <v>1601.282299830926</v>
+        <v>1662.698262194183</v>
       </c>
       <c r="I104">
-        <v>1130.378605908403</v>
+        <v>1167.276575259848</v>
       </c>
       <c r="J104">
-        <v>2092.59091603516</v>
+        <v>2173.267845305344</v>
       </c>
       <c r="K104">
-        <v>2060.940927877671</v>
+        <v>2119.91129162468</v>
       </c>
       <c r="L104">
-        <v>1589.548983474986</v>
+        <v>1625.271782818241</v>
       </c>
       <c r="M104">
-        <v>2552.26053557871</v>
+        <v>2630.690410592686</v>
       </c>
     </row>
     <row r="105">
@@ -5499,22 +5499,22 @@
         <v>660.997321740644</v>
       </c>
       <c r="H105">
-        <v>2199.82793762738</v>
+        <v>2314.788230909669</v>
       </c>
       <c r="I105">
-        <v>1365.236626625785</v>
+        <v>1466.356536325905</v>
       </c>
       <c r="J105">
-        <v>3103.904300867381</v>
+        <v>3243.9950161829</v>
       </c>
       <c r="K105">
-        <v>2817.073064847807</v>
+        <v>2933.26996516729</v>
       </c>
       <c r="L105">
-        <v>1974.745856689052</v>
+        <v>2076.261856418573</v>
       </c>
       <c r="M105">
-        <v>3726.64146219378</v>
+        <v>3859.667462092374</v>
       </c>
     </row>
     <row r="106">
@@ -5548,22 +5548,22 @@
         <v>876.3372788402429</v>
       </c>
       <c r="H106">
-        <v>1283.574694103695</v>
+        <v>1353.823056786304</v>
       </c>
       <c r="I106">
-        <v>903.5138839800785</v>
+        <v>933.5234285322204</v>
       </c>
       <c r="J106">
-        <v>1684.107934682503</v>
+        <v>1795.489298602485</v>
       </c>
       <c r="K106">
-        <v>2066.927698588732</v>
+        <v>2135.702775875667</v>
       </c>
       <c r="L106">
-        <v>1676.332597751209</v>
+        <v>1710.944735620021</v>
       </c>
       <c r="M106">
-        <v>2473.474964423868</v>
+        <v>2583.652447715563</v>
       </c>
     </row>
     <row r="107">
@@ -5597,22 +5597,22 @@
         <v>833.9249787986645</v>
       </c>
       <c r="H107">
-        <v>942.5856875524869</v>
+        <v>979.4360494602993</v>
       </c>
       <c r="I107">
-        <v>561.6062491487377</v>
+        <v>590.3417733957265</v>
       </c>
       <c r="J107">
-        <v>1325.333439240197</v>
+        <v>1370.435327353864</v>
       </c>
       <c r="K107">
-        <v>1687.622323509744</v>
+        <v>1725.048990594189</v>
       </c>
       <c r="L107">
-        <v>1292.338298570308</v>
+        <v>1318.299679064468</v>
       </c>
       <c r="M107">
-        <v>2078.769032153913</v>
+        <v>2123.444973866148</v>
       </c>
     </row>
     <row r="108">
@@ -5646,22 +5646,22 @@
         <v>936.7087766839763</v>
       </c>
       <c r="H108">
-        <v>1284.277410781673</v>
+        <v>1246.006063406732</v>
       </c>
       <c r="I108">
-        <v>816.0349862515446</v>
+        <v>810.1292105456363</v>
       </c>
       <c r="J108">
-        <v>1780.891579867474</v>
+        <v>1709.777067819038</v>
       </c>
       <c r="K108">
-        <v>2120.788521960879</v>
+        <v>2083.640985732667</v>
       </c>
       <c r="L108">
-        <v>1651.367246657532</v>
+        <v>1639.021927391618</v>
       </c>
       <c r="M108">
-        <v>2622.786520166487</v>
+        <v>2553.964055423807</v>
       </c>
     </row>
     <row r="109">
@@ -5695,22 +5695,22 @@
         <v>958.9735603551385</v>
       </c>
       <c r="H109">
-        <v>1247.807119024974</v>
+        <v>1261.908601074852</v>
       </c>
       <c r="I109">
-        <v>791.8359361264568</v>
+        <v>816.1728674348939</v>
       </c>
       <c r="J109">
-        <v>1716.265776385842</v>
+        <v>1720.776323786715</v>
       </c>
       <c r="K109">
-        <v>2107.335430253966</v>
+        <v>2123.85562499774</v>
       </c>
       <c r="L109">
-        <v>1644.250799067139</v>
+        <v>1660.554224898146</v>
       </c>
       <c r="M109">
-        <v>2588.690326394684</v>
+        <v>2591.840787029934</v>
       </c>
     </row>
     <row r="110">
@@ -5744,22 +5744,22 @@
         <v>774.9477438897786</v>
       </c>
       <c r="H110">
-        <v>1443.922915251625</v>
+        <v>1477.83805255371</v>
       </c>
       <c r="I110">
-        <v>1042.316347324163</v>
+        <v>1077.222614662421</v>
       </c>
       <c r="J110">
-        <v>1847.233377097529</v>
+        <v>1884.244110049269</v>
       </c>
       <c r="K110">
-        <v>2100.014866433454</v>
+        <v>2135.767689159399</v>
       </c>
       <c r="L110">
-        <v>1691.820402914032</v>
+        <v>1717.114813612041</v>
       </c>
       <c r="M110">
-        <v>2529.121026942293</v>
+        <v>2563.134976069839</v>
       </c>
     </row>
     <row r="111">
@@ -5793,22 +5793,22 @@
         <v>884.7538260536794</v>
       </c>
       <c r="H111">
-        <v>1461.034147401065</v>
+        <v>1525.16057041728</v>
       </c>
       <c r="I111">
-        <v>954.4380977073911</v>
+        <v>1027.411720775979</v>
       </c>
       <c r="J111">
-        <v>1978.469426889076</v>
+        <v>2037.529426039023</v>
       </c>
       <c r="K111">
-        <v>2220.119243460807</v>
+        <v>2282.528247053473</v>
       </c>
       <c r="L111">
-        <v>1700.38296199286</v>
+        <v>1770.479300381312</v>
       </c>
       <c r="M111">
-        <v>2749.355866782368</v>
+        <v>2809.6630433593</v>
       </c>
     </row>
     <row r="112">
@@ -5842,22 +5842,22 @@
         <v>540.4279046387808</v>
       </c>
       <c r="H112">
-        <v>884.5985462562445</v>
+        <v>933.3728103217516</v>
       </c>
       <c r="I112">
-        <v>633.9527787872838</v>
+        <v>660.1027212246944</v>
       </c>
       <c r="J112">
-        <v>1138.374039581368</v>
+        <v>1217.026972051483</v>
       </c>
       <c r="K112">
-        <v>1362.862966252395</v>
+        <v>1412.209158598123</v>
       </c>
       <c r="L112">
-        <v>1105.52924008545</v>
+        <v>1128.248349823627</v>
       </c>
       <c r="M112">
-        <v>1624.4818495875</v>
+        <v>1704.302229098914</v>
       </c>
     </row>
     <row r="113">
@@ -5891,22 +5891,22 @@
         <v>580.6367463355934</v>
       </c>
       <c r="H113">
-        <v>1386.760230851787</v>
+        <v>1395.188515543642</v>
       </c>
       <c r="I113">
-        <v>873.9827168092094</v>
+        <v>901.4374830639551</v>
       </c>
       <c r="J113">
-        <v>1937.289832061848</v>
+        <v>1917.813507993052</v>
       </c>
       <c r="K113">
-        <v>1904.642443409574</v>
+        <v>1912.760856778088</v>
       </c>
       <c r="L113">
-        <v>1390.491155200291</v>
+        <v>1413.526018140093</v>
       </c>
       <c r="M113">
-        <v>2456.775653998335</v>
+        <v>2439.533377830786</v>
       </c>
     </row>
     <row r="114">
@@ -5940,22 +5940,22 @@
         <v>2735.332323717093</v>
       </c>
       <c r="H114">
-        <v>910.9681489920149</v>
+        <v>978.4011507115169</v>
       </c>
       <c r="I114">
-        <v>575.0440246650542</v>
+        <v>599.5595606054867</v>
       </c>
       <c r="J114">
-        <v>1280.550304010933</v>
+        <v>1389.864019238576</v>
       </c>
       <c r="K114">
-        <v>3399.430177319745</v>
+        <v>3465.45591105587</v>
       </c>
       <c r="L114">
-        <v>2971.070059597796</v>
+        <v>3007.605400644542</v>
       </c>
       <c r="M114">
-        <v>3828.857190385211</v>
+        <v>3934.737285437038</v>
       </c>
     </row>
     <row r="115">
@@ -5989,22 +5989,22 @@
         <v>2102.994932380647</v>
       </c>
       <c r="H115">
-        <v>1229.961152554929</v>
+        <v>1198.10623423498</v>
       </c>
       <c r="I115">
-        <v>691.9935727850785</v>
+        <v>710.8933541308953</v>
       </c>
       <c r="J115">
-        <v>1868.340323649733</v>
+        <v>1753.081693387989</v>
       </c>
       <c r="K115">
-        <v>3128.055635809008</v>
+        <v>3097.461707045136</v>
       </c>
       <c r="L115">
-        <v>2553.156149721987</v>
+        <v>2565.669397285144</v>
       </c>
       <c r="M115">
-        <v>3803.713111524563</v>
+        <v>3687.733945980916</v>
       </c>
     </row>
     <row r="116">
@@ -6038,22 +6038,22 @@
         <v>724.2830872727983</v>
       </c>
       <c r="H116">
-        <v>1211.373503897023</v>
+        <v>1352.238291707279</v>
       </c>
       <c r="I116">
-        <v>765.5574007648285</v>
+        <v>831.4337729929846</v>
       </c>
       <c r="J116">
-        <v>1687.992923998489</v>
+        <v>1910.088518687051</v>
       </c>
       <c r="K116">
-        <v>1832.692083531131</v>
+        <v>1973.187082148889</v>
       </c>
       <c r="L116">
-        <v>1376.032236141254</v>
+        <v>1445.417287294636</v>
       </c>
       <c r="M116">
-        <v>2319.716501699081</v>
+        <v>2533.115575081072</v>
       </c>
     </row>
     <row r="117">
@@ -6087,22 +6087,22 @@
         <v>690.3754738307325</v>
       </c>
       <c r="H117">
-        <v>944.713872341749</v>
+        <v>1044.014712238392</v>
       </c>
       <c r="I117">
-        <v>576.7960256074082</v>
+        <v>634.9147022871555</v>
       </c>
       <c r="J117">
-        <v>1327.749589754354</v>
+        <v>1468.540668965239</v>
       </c>
       <c r="K117">
-        <v>1530.980479347334</v>
+        <v>1629.14575739223</v>
       </c>
       <c r="L117">
-        <v>1151.471537383958</v>
+        <v>1204.662566916051</v>
       </c>
       <c r="M117">
-        <v>1928.215147436392</v>
+        <v>2068.903091784276</v>
       </c>
     </row>
     <row r="118">
@@ -6136,22 +6136,22 @@
         <v>493.294875264108</v>
       </c>
       <c r="H118">
-        <v>910.0787145292575</v>
+        <v>933.2880793647516</v>
       </c>
       <c r="I118">
-        <v>591.9077399188084</v>
+        <v>589.7505590113707</v>
       </c>
       <c r="J118">
-        <v>1237.93766914098</v>
+        <v>1299.171631963527</v>
       </c>
       <c r="K118">
-        <v>1294.985601550572</v>
+        <v>1317.94833974086</v>
       </c>
       <c r="L118">
-        <v>955.053931945744</v>
+        <v>952.6557980168615</v>
       </c>
       <c r="M118">
-        <v>1637.267831314454</v>
+        <v>1703.097077023133</v>
       </c>
     </row>
     <row r="119">
@@ -6185,22 +6185,22 @@
         <v>443.1316536754208</v>
       </c>
       <c r="H119">
-        <v>919.285559615025</v>
+        <v>939.9804243898792</v>
       </c>
       <c r="I119">
-        <v>550.471829852921</v>
+        <v>576.853349423349</v>
       </c>
       <c r="J119">
-        <v>1329.297993923474</v>
+        <v>1340.695212343351</v>
       </c>
       <c r="K119">
-        <v>1270.684257988865</v>
+        <v>1292.725447230242</v>
       </c>
       <c r="L119">
-        <v>890.3104952438807</v>
+        <v>913.8838527777374</v>
       </c>
       <c r="M119">
-        <v>1690.34183897274</v>
+        <v>1694.997479659482</v>
       </c>
     </row>
     <row r="120">
@@ -6234,22 +6234,22 @@
         <v>925.1179325587761</v>
       </c>
       <c r="H120">
-        <v>1046.162129061688</v>
+        <v>1074.757865269617</v>
       </c>
       <c r="I120">
-        <v>684.3437131828907</v>
+        <v>712.5738501870425</v>
       </c>
       <c r="J120">
-        <v>1429.544638881797</v>
+        <v>1459.161162745313</v>
       </c>
       <c r="K120">
-        <v>1808.827523146801</v>
+        <v>1839.872468250392</v>
       </c>
       <c r="L120">
-        <v>1404.499541754014</v>
+        <v>1437.976404757223</v>
       </c>
       <c r="M120">
-        <v>2230.865602600842</v>
+        <v>2261.268768090974</v>
       </c>
     </row>
     <row r="121">
@@ -6283,22 +6283,22 @@
         <v>899.2072735838229</v>
       </c>
       <c r="H121">
-        <v>1639.573032557925</v>
+        <v>1819.337430809106</v>
       </c>
       <c r="I121">
-        <v>1055.346693116882</v>
+        <v>1179.045836445734</v>
       </c>
       <c r="J121">
-        <v>2249.322228154434</v>
+        <v>2477.948438899336</v>
       </c>
       <c r="K121">
-        <v>2375.397328056125</v>
+        <v>2555.837670692202</v>
       </c>
       <c r="L121">
-        <v>1764.2375415718</v>
+        <v>1886.63213573602</v>
       </c>
       <c r="M121">
-        <v>3001.625344830199</v>
+        <v>3238.249102198745</v>
       </c>
     </row>
     <row r="122">
@@ -6332,22 +6332,22 @@
         <v>1044.905990986284</v>
       </c>
       <c r="H122">
-        <v>1008.662761564804</v>
+        <v>1063.859967838668</v>
       </c>
       <c r="I122">
-        <v>723.5621877432549</v>
+        <v>751.3913760842061</v>
       </c>
       <c r="J122">
-        <v>1294.72817529028</v>
+        <v>1377.289255342045</v>
       </c>
       <c r="K122">
-        <v>1980.78516483608</v>
+        <v>2036.354700026797</v>
       </c>
       <c r="L122">
-        <v>1685.756681065534</v>
+        <v>1717.212518168327</v>
       </c>
       <c r="M122">
-        <v>2277.073504722706</v>
+        <v>2359.748567588024</v>
       </c>
     </row>
     <row r="123">
@@ -6381,22 +6381,22 @@
         <v>1108.105143428313</v>
       </c>
       <c r="H123">
-        <v>1804.156496786288</v>
+        <v>1762.649017462412</v>
       </c>
       <c r="I123">
-        <v>1226.224753285576</v>
+        <v>1217.212267241641</v>
       </c>
       <c r="J123">
-        <v>2390.761328258513</v>
+        <v>2310.411100806325</v>
       </c>
       <c r="K123">
-        <v>2838.914441724123</v>
+        <v>2794.928625480031</v>
       </c>
       <c r="L123">
-        <v>2263.509703582246</v>
+        <v>2248.477837858961</v>
       </c>
       <c r="M123">
-        <v>3427.857126672146</v>
+        <v>3348.507890925855</v>
       </c>
     </row>
     <row r="124">
@@ -6430,22 +6430,22 @@
         <v>1360.576582325545</v>
       </c>
       <c r="H124">
-        <v>1033.333251096207</v>
+        <v>1048.141784161261</v>
       </c>
       <c r="I124">
-        <v>698.2527670766186</v>
+        <v>698.4183241843643</v>
       </c>
       <c r="J124">
-        <v>1388.352415835959</v>
+        <v>1412.55577747906</v>
       </c>
       <c r="K124">
-        <v>2269.631506749163</v>
+        <v>2283.018262283525</v>
       </c>
       <c r="L124">
-        <v>1903.679082538078</v>
+        <v>1915.025819942283</v>
       </c>
       <c r="M124">
-        <v>2645.217288314792</v>
+        <v>2668.367739597106</v>
       </c>
     </row>
     <row r="125">
@@ -6479,22 +6479,22 @@
         <v>1074.816859590707</v>
       </c>
       <c r="H125">
-        <v>1661.151000358602</v>
+        <v>1719.886183355443</v>
       </c>
       <c r="I125">
-        <v>1037.752952158388</v>
+        <v>1081.201743956266</v>
       </c>
       <c r="J125">
-        <v>2361.872500687478</v>
+        <v>2417.42903055786</v>
       </c>
       <c r="K125">
-        <v>2634.541479506822</v>
+        <v>2695.845606095317</v>
       </c>
       <c r="L125">
-        <v>1999.476119770047</v>
+        <v>2046.534245150367</v>
       </c>
       <c r="M125">
-        <v>3351.766612460968</v>
+        <v>3393.40599262972</v>
       </c>
     </row>
     <row r="126">
@@ -6528,22 +6528,22 @@
         <v>1308.399320349187</v>
       </c>
       <c r="H126">
-        <v>1507.170755567734</v>
+        <v>1541.998264963574</v>
       </c>
       <c r="I126">
-        <v>1066.529039659388</v>
+        <v>1087.130791047474</v>
       </c>
       <c r="J126">
-        <v>1963.965268259027</v>
+        <v>2027.650140351035</v>
       </c>
       <c r="K126">
-        <v>2665.295954285536</v>
+        <v>2699.712035363506</v>
       </c>
       <c r="L126">
-        <v>2201.264177387575</v>
+        <v>2219.261267882611</v>
       </c>
       <c r="M126">
-        <v>3148.269248736483</v>
+        <v>3208.727877353695</v>
       </c>
     </row>
     <row r="127">
@@ -6577,22 +6577,22 @@
         <v>1435.698559850197</v>
       </c>
       <c r="H127">
-        <v>2421.780210598346</v>
+        <v>2561.857561499478</v>
       </c>
       <c r="I127">
-        <v>1638.445074703876</v>
+        <v>1732.345203892308</v>
       </c>
       <c r="J127">
-        <v>3212.270910051855</v>
+        <v>3390.068162817025</v>
       </c>
       <c r="K127">
-        <v>3699.600024785237</v>
+        <v>3839.883798597605</v>
       </c>
       <c r="L127">
-        <v>2892.913418436001</v>
+        <v>2999.505207475005</v>
       </c>
       <c r="M127">
-        <v>4505.599851785294</v>
+        <v>4691.694530027235</v>
       </c>
     </row>
     <row r="128">
@@ -6626,22 +6626,22 @@
         <v>476.6074644388343</v>
       </c>
       <c r="H128">
-        <v>1237.726370483623</v>
+        <v>1255.020796604379</v>
       </c>
       <c r="I128">
-        <v>899.8480948767476</v>
+        <v>927.7063920845114</v>
       </c>
       <c r="J128">
-        <v>1555.825964317382</v>
+        <v>1570.128449953183</v>
       </c>
       <c r="K128">
-        <v>1635.248167684718</v>
+        <v>1652.802473967027</v>
       </c>
       <c r="L128">
-        <v>1291.581421654991</v>
+        <v>1319.742144562635</v>
       </c>
       <c r="M128">
-        <v>1964.166301765383</v>
+        <v>1979.915608729895</v>
       </c>
     </row>
     <row r="129">
@@ -6675,22 +6675,22 @@
         <v>650.4582590249113</v>
       </c>
       <c r="H129">
-        <v>1197.168144288186</v>
+        <v>1248.884878932758</v>
       </c>
       <c r="I129">
-        <v>801.4654567936549</v>
+        <v>830.9394541085931</v>
       </c>
       <c r="J129">
-        <v>1619.51885605375</v>
+        <v>1690.723841213497</v>
       </c>
       <c r="K129">
-        <v>1757.281476893666</v>
+        <v>1809.374410571287</v>
       </c>
       <c r="L129">
-        <v>1351.723780785477</v>
+        <v>1381.192876493163</v>
       </c>
       <c r="M129">
-        <v>2187.935369198131</v>
+        <v>2258.853587184847</v>
       </c>
     </row>
     <row r="130">
@@ -6724,22 +6724,22 @@
         <v>899.0066899211962</v>
       </c>
       <c r="H130">
-        <v>1656.828895249552</v>
+        <v>1768.996417604127</v>
       </c>
       <c r="I130">
-        <v>1200.226234621374</v>
+        <v>1265.407201934366</v>
       </c>
       <c r="J130">
-        <v>2151.147609007632</v>
+        <v>2321.880915393851</v>
       </c>
       <c r="K130">
-        <v>2463.144443757452</v>
+        <v>2576.577460630086</v>
       </c>
       <c r="L130">
-        <v>2000.689338183668</v>
+        <v>2072.066225010911</v>
       </c>
       <c r="M130">
-        <v>2965.124539409938</v>
+        <v>3131.510351351859</v>
       </c>
     </row>
     <row r="131">
@@ -6773,22 +6773,22 @@
         <v>943.039241833093</v>
       </c>
       <c r="H131">
-        <v>1443.111745492676</v>
+        <v>1595.853672962378</v>
       </c>
       <c r="I131">
-        <v>959.671907520439</v>
+        <v>1080.632793527187</v>
       </c>
       <c r="J131">
-        <v>1950.500454953637</v>
+        <v>2125.229251150702</v>
       </c>
       <c r="K131">
-        <v>2292.801158977395</v>
+        <v>2445.250677770341</v>
       </c>
       <c r="L131">
-        <v>1805.012547958701</v>
+        <v>1918.574208469515</v>
       </c>
       <c r="M131">
-        <v>2814.186017090665</v>
+        <v>2990.045238951505</v>
       </c>
     </row>
     <row r="132">
@@ -6822,22 +6822,22 @@
         <v>1244.193851554126</v>
       </c>
       <c r="H132">
-        <v>1672.360696783408</v>
+        <v>1693.627790092361</v>
       </c>
       <c r="I132">
-        <v>1161.360093070531</v>
+        <v>1151.996346009415</v>
       </c>
       <c r="J132">
-        <v>2196.653918067651</v>
+        <v>2254.79910131938</v>
       </c>
       <c r="K132">
-        <v>2788.623346141374</v>
+        <v>2813.476247739931</v>
       </c>
       <c r="L132">
-        <v>2262.813250024176</v>
+        <v>2256.333883492354</v>
       </c>
       <c r="M132">
-        <v>3320.092843945755</v>
+        <v>3380.322675202205</v>
       </c>
     </row>
     <row r="133">
@@ -6871,22 +6871,22 @@
         <v>1428.562884028717</v>
       </c>
       <c r="H133">
-        <v>1566.419667799546</v>
+        <v>1695.542553073103</v>
       </c>
       <c r="I133">
-        <v>954.4655867759064</v>
+        <v>1051.827401951815</v>
       </c>
       <c r="J133">
-        <v>2181.842440068442</v>
+        <v>2356.270409376604</v>
       </c>
       <c r="K133">
-        <v>2854.51020831293</v>
+        <v>2980.832611983646</v>
       </c>
       <c r="L133">
-        <v>2230.035817337721</v>
+        <v>2325.272720195104</v>
       </c>
       <c r="M133">
-        <v>3487.208030127581</v>
+        <v>3651.664322739776</v>
       </c>
     </row>
     <row r="134">
@@ -6920,22 +6920,22 @@
         <v>973.764147742223</v>
       </c>
       <c r="H134">
-        <v>1407.358284596052</v>
+        <v>1424.781729104942</v>
       </c>
       <c r="I134">
-        <v>969.6434042407241</v>
+        <v>974.2320100877154</v>
       </c>
       <c r="J134">
-        <v>1880.027721956417</v>
+        <v>1911.365434902347</v>
       </c>
       <c r="K134">
-        <v>2242.350361447911</v>
+        <v>2259.403476116399</v>
       </c>
       <c r="L134">
-        <v>1776.070178114667</v>
+        <v>1784.495198623051</v>
       </c>
       <c r="M134">
-        <v>2723.776931872913</v>
+        <v>2756.62559519171</v>
       </c>
     </row>
     <row r="135">
@@ -6969,22 +6969,22 @@
         <v>910.8080740531622</v>
       </c>
       <c r="H135">
-        <v>1169.469198663359</v>
+        <v>1345.607427200893</v>
       </c>
       <c r="I135">
-        <v>719.0254332532419</v>
+        <v>827.7054166922998</v>
       </c>
       <c r="J135">
-        <v>1620.168921606395</v>
+        <v>1860.382753624375</v>
       </c>
       <c r="K135">
-        <v>1952.810083904898</v>
+        <v>2126.400588884907</v>
       </c>
       <c r="L135">
-        <v>1488.01444967697</v>
+        <v>1595.295351369969</v>
       </c>
       <c r="M135">
-        <v>2417.950303369486</v>
+        <v>2657.041712899123</v>
       </c>
     </row>
     <row r="136">
@@ -7018,22 +7018,22 @@
         <v>1181.154365018692</v>
       </c>
       <c r="H136">
-        <v>1879.476305020512</v>
+        <v>2060.713798653218</v>
       </c>
       <c r="I136">
-        <v>1218.957000222355</v>
+        <v>1309.669932742264</v>
       </c>
       <c r="J136">
-        <v>2545.761871691232</v>
+        <v>2822.415958991279</v>
       </c>
       <c r="K136">
-        <v>2844.077295179261</v>
+        <v>3023.786151358118</v>
       </c>
       <c r="L136">
-        <v>2157.856442614434</v>
+        <v>2253.990301296996</v>
       </c>
       <c r="M136">
-        <v>3553.730701091414</v>
+        <v>3821.06951998094</v>
       </c>
     </row>
     <row r="137">
@@ -7067,22 +7067,22 @@
         <v>1023.999260204048</v>
       </c>
       <c r="H137">
-        <v>1735.407396557562</v>
+        <v>1825.772053982607</v>
       </c>
       <c r="I137">
-        <v>1101.455081367681</v>
+        <v>1142.705397942168</v>
       </c>
       <c r="J137">
-        <v>2420.098145353395</v>
+        <v>2562.992054044337</v>
       </c>
       <c r="K137">
-        <v>2573.554259843942</v>
+        <v>2665.48290984773</v>
       </c>
       <c r="L137">
-        <v>1921.234120915254</v>
+        <v>1952.360712383521</v>
       </c>
       <c r="M137">
-        <v>3287.520698410875</v>
+        <v>3425.055911785089</v>
       </c>
     </row>
     <row r="138">
@@ -7116,22 +7116,22 @@
         <v>557.1837329272945</v>
       </c>
       <c r="H138">
-        <v>1412.674115863055</v>
+        <v>1434.48666433155</v>
       </c>
       <c r="I138">
-        <v>1129.811564590268</v>
+        <v>1147.549355636269</v>
       </c>
       <c r="J138">
-        <v>1692.051431364087</v>
+        <v>1723.947775490656</v>
       </c>
       <c r="K138">
-        <v>1932.837694583813</v>
+        <v>1954.196566370821</v>
       </c>
       <c r="L138">
-        <v>1650.412540283948</v>
+        <v>1664.560744570463</v>
       </c>
       <c r="M138">
-        <v>2215.994432417176</v>
+        <v>2246.638328039738</v>
       </c>
     </row>
     <row r="139">
@@ -7165,22 +7165,22 @@
         <v>686.2185093107089</v>
       </c>
       <c r="H139">
-        <v>1186.397235654202</v>
+        <v>1304.562609314125</v>
       </c>
       <c r="I139">
-        <v>800.0464471028514</v>
+        <v>858.0148118978474</v>
       </c>
       <c r="J139">
-        <v>1580.42721717104</v>
+        <v>1782.341838372041</v>
       </c>
       <c r="K139">
-        <v>1829.207135831338</v>
+        <v>1946.622668165373</v>
       </c>
       <c r="L139">
-        <v>1443.312928648666</v>
+        <v>1501.001435513908</v>
       </c>
       <c r="M139">
-        <v>2230.055721529944</v>
+        <v>2425.529597004572</v>
       </c>
     </row>
     <row r="140">
@@ -7214,22 +7214,22 @@
         <v>581.7709766537772</v>
       </c>
       <c r="H140">
-        <v>1462.512409008579</v>
+        <v>1553.752093067198</v>
       </c>
       <c r="I140">
-        <v>1078.638539532786</v>
+        <v>1139.081637708158</v>
       </c>
       <c r="J140">
-        <v>1855.891082991104</v>
+        <v>1982.900569264981</v>
       </c>
       <c r="K140">
-        <v>1959.554258412362</v>
+        <v>2050.742077736962</v>
       </c>
       <c r="L140">
-        <v>1565.810127939855</v>
+        <v>1630.814889310746</v>
       </c>
       <c r="M140">
-        <v>2363.342588148641</v>
+        <v>2485.734919223872</v>
       </c>
     </row>
     <row r="141">
@@ -7263,22 +7263,22 @@
         <v>571.4538428617341</v>
       </c>
       <c r="H141">
-        <v>1428.31683408104</v>
+        <v>1504.545416855226</v>
       </c>
       <c r="I141">
-        <v>952.2654456597572</v>
+        <v>1032.245198460841</v>
       </c>
       <c r="J141">
-        <v>1964.757404995323</v>
+        <v>2019.500870988204</v>
       </c>
       <c r="K141">
-        <v>1916.950596201767</v>
+        <v>1993.401471326803</v>
       </c>
       <c r="L141">
-        <v>1443.044478511648</v>
+        <v>1517.454547328758</v>
       </c>
       <c r="M141">
-        <v>2454.947782854852</v>
+        <v>2515.646667403139</v>
       </c>
     </row>
     <row r="142">
@@ -7312,22 +7312,22 @@
         <v>1114.192232397169</v>
       </c>
       <c r="H142">
-        <v>1225.524561515659</v>
+        <v>1298.464916057311</v>
       </c>
       <c r="I142">
-        <v>911.2347301522834</v>
+        <v>944.6770365586899</v>
       </c>
       <c r="J142">
-        <v>1532.561543362085</v>
+        <v>1644.008724316807</v>
       </c>
       <c r="K142">
-        <v>2248.981144638676</v>
+        <v>2323.227519425513</v>
       </c>
       <c r="L142">
-        <v>1927.200800508562</v>
+        <v>1958.005629020705</v>
       </c>
       <c r="M142">
-        <v>2568.505932809915</v>
+        <v>2679.653578035493</v>
       </c>
     </row>
     <row r="143">
@@ -7361,22 +7361,22 @@
         <v>1060.374578822517</v>
       </c>
       <c r="H143">
-        <v>1373.564076779659</v>
+        <v>1468.08708039742</v>
       </c>
       <c r="I143">
-        <v>929.8458878370102</v>
+        <v>1003.553473518575</v>
       </c>
       <c r="J143">
-        <v>1840.489305103176</v>
+        <v>1957.044254968074</v>
       </c>
       <c r="K143">
-        <v>2349.736168382739</v>
+        <v>2442.960182459232</v>
       </c>
       <c r="L143">
-        <v>1894.148879343843</v>
+        <v>1970.950482303656</v>
       </c>
       <c r="M143">
-        <v>2825.458265136756</v>
+        <v>2944.326787555884</v>
       </c>
     </row>
     <row r="144">
@@ -7410,22 +7410,22 @@
         <v>723.9682086785185</v>
       </c>
       <c r="H144">
-        <v>1646.203510439301</v>
+        <v>1713.631275751146</v>
       </c>
       <c r="I144">
-        <v>1155.104404557748</v>
+        <v>1208.613457187807</v>
       </c>
       <c r="J144">
-        <v>2149.224724635375</v>
+        <v>2236.766155036645</v>
       </c>
       <c r="K144">
-        <v>2141.304242062265</v>
+        <v>2210.02785101331</v>
       </c>
       <c r="L144">
-        <v>1605.85935342496</v>
+        <v>1661.75966822143</v>
       </c>
       <c r="M144">
-        <v>2697.114734188885</v>
+        <v>2781.789634588923</v>
       </c>
     </row>
     <row r="145">
@@ -7459,22 +7459,22 @@
         <v>610.4104323429279</v>
       </c>
       <c r="H145">
-        <v>2173.242545180345</v>
+        <v>2376.707648693351</v>
       </c>
       <c r="I145">
-        <v>1447.336532646106</v>
+        <v>1586.970019303595</v>
       </c>
       <c r="J145">
-        <v>2938.351360193638</v>
+        <v>3200.58716548794</v>
       </c>
       <c r="K145">
-        <v>2592.925943246352</v>
+        <v>2796.361601096598</v>
       </c>
       <c r="L145">
-        <v>1848.911137896928</v>
+        <v>1992.707948224694</v>
       </c>
       <c r="M145">
-        <v>3380.428725033808</v>
+        <v>3640.785728489281</v>
       </c>
     </row>
     <row r="146">
@@ -7508,22 +7508,22 @@
         <v>155.9598778471054</v>
       </c>
       <c r="H146">
-        <v>929.0260841365487</v>
+        <v>953.361024405709</v>
       </c>
       <c r="I146">
-        <v>660.8448669073199</v>
+        <v>673.1542785566685</v>
       </c>
       <c r="J146">
-        <v>1191.642112743257</v>
+        <v>1225.354453543948</v>
       </c>
       <c r="K146">
-        <v>1066.910869324005</v>
+        <v>1091.540437708732</v>
       </c>
       <c r="L146">
-        <v>797.2310992609218</v>
+        <v>809.9441474163135</v>
       </c>
       <c r="M146">
-        <v>1329.584939693658</v>
+        <v>1365.014551361956</v>
       </c>
     </row>
     <row r="147">
@@ -7557,22 +7557,22 @@
         <v>257.7715709615361</v>
       </c>
       <c r="H147">
-        <v>2057.89355131917</v>
+        <v>2276.301212020803</v>
       </c>
       <c r="I147">
-        <v>1529.370021052458</v>
+        <v>1682.306662251022</v>
       </c>
       <c r="J147">
-        <v>2592.330309258857</v>
+        <v>2872.36644513754</v>
       </c>
       <c r="K147">
-        <v>2288.733434422116</v>
+        <v>2508.097771959005</v>
       </c>
       <c r="L147">
-        <v>1758.5521842192</v>
+        <v>1914.412328302402</v>
       </c>
       <c r="M147">
-        <v>2826.485272782116</v>
+        <v>3101.523961857983</v>
       </c>
     </row>
     <row r="148">
@@ -7606,22 +7606,22 @@
         <v>408.7952230750003</v>
       </c>
       <c r="H148">
-        <v>1568.794747721485</v>
+        <v>1563.02743727082</v>
       </c>
       <c r="I148">
-        <v>1345.920745192335</v>
+        <v>1340.357276052875</v>
       </c>
       <c r="J148">
-        <v>1792.028274722701</v>
+        <v>1785.407300314019</v>
       </c>
       <c r="K148">
-        <v>1962.523593711822</v>
+        <v>1957.5195568983</v>
       </c>
       <c r="L148">
-        <v>1738.235809341602</v>
+        <v>1732.134817097385</v>
       </c>
       <c r="M148">
-        <v>2184.11234342091</v>
+        <v>2179.939596658764</v>
       </c>
     </row>
     <row r="149">
@@ -7655,22 +7655,22 @@
         <v>512.6843184365587</v>
       </c>
       <c r="H149">
-        <v>2450.193683830089</v>
+        <v>2724.007892027671</v>
       </c>
       <c r="I149">
-        <v>2036.369347049662</v>
+        <v>2285.090753577395</v>
       </c>
       <c r="J149">
-        <v>2870.631954377572</v>
+        <v>3170.911183706431</v>
       </c>
       <c r="K149">
-        <v>2945.70848804657</v>
+        <v>3220.017926116489</v>
       </c>
       <c r="L149">
-        <v>2531.945767800608</v>
+        <v>2780.685890044429</v>
       </c>
       <c r="M149">
-        <v>3364.834891090527</v>
+        <v>3668.880619543787</v>
       </c>
     </row>
     <row r="150">
@@ -7704,22 +7704,22 @@
         <v>932.816407396875</v>
       </c>
       <c r="H150">
-        <v>1081.66668820601</v>
+        <v>1075.847140825689</v>
       </c>
       <c r="I150">
-        <v>697.2135203985168</v>
+        <v>696.8475775269832</v>
       </c>
       <c r="J150">
-        <v>1489.740513764336</v>
+        <v>1479.797573271333</v>
       </c>
       <c r="K150">
-        <v>1863.588546696128</v>
+        <v>1857.410426599182</v>
       </c>
       <c r="L150">
-        <v>1450.397920201867</v>
+        <v>1449.841465559249</v>
       </c>
       <c r="M150">
-        <v>2296.780200625198</v>
+        <v>2286.496661458738</v>
       </c>
     </row>
     <row r="151">
@@ -7753,22 +7753,22 @@
         <v>1259.048151158878</v>
       </c>
       <c r="H151">
-        <v>1055.31515143738</v>
+        <v>1265.878962400245</v>
       </c>
       <c r="I151">
-        <v>667.2789284280184</v>
+        <v>791.8995230240511</v>
       </c>
       <c r="J151">
-        <v>1476.479541260683</v>
+        <v>1792.905748340953</v>
       </c>
       <c r="K151">
-        <v>2140.943686209846</v>
+        <v>2351.136808805321</v>
       </c>
       <c r="L151">
-        <v>1709.652837806764</v>
+        <v>1836.590995712193</v>
       </c>
       <c r="M151">
-        <v>2606.0840428894</v>
+        <v>2914.22356697444</v>
       </c>
     </row>
     <row r="152">
@@ -7802,22 +7802,22 @@
         <v>627.157002898223</v>
       </c>
       <c r="H152">
-        <v>1601.106918569797</v>
+        <v>1621.109389583441</v>
       </c>
       <c r="I152">
-        <v>1241.995761591384</v>
+        <v>1254.873196852102</v>
       </c>
       <c r="J152">
-        <v>1973.29155388914</v>
+        <v>2000.299625085577</v>
       </c>
       <c r="K152">
-        <v>2190.214681433506</v>
+        <v>2210.607291107628</v>
       </c>
       <c r="L152">
-        <v>1827.98931840456</v>
+        <v>1838.577845874383</v>
       </c>
       <c r="M152">
-        <v>2565.323642171404</v>
+        <v>2593.272033926723</v>
       </c>
     </row>
     <row r="153">
@@ -7851,22 +7851,22 @@
         <v>833.2056499854851</v>
       </c>
       <c r="H153">
-        <v>2009.401287001422</v>
+        <v>2290.782008713876</v>
       </c>
       <c r="I153">
-        <v>1456.498675051809</v>
+        <v>1663.578754150693</v>
       </c>
       <c r="J153">
-        <v>2570.673484413528</v>
+        <v>2926.280470307446</v>
       </c>
       <c r="K153">
-        <v>2797.159183478985</v>
+        <v>3078.502464072552</v>
       </c>
       <c r="L153">
-        <v>2238.781326233579</v>
+        <v>2448.425567259272</v>
       </c>
       <c r="M153">
-        <v>3355.524919924972</v>
+        <v>3715.039107251688</v>
       </c>
     </row>
     <row r="154">
@@ -7900,22 +7900,22 @@
         <v>1121.8261953281</v>
       </c>
       <c r="H154">
-        <v>1877.333303329016</v>
+        <v>1885.283126566129</v>
       </c>
       <c r="I154">
-        <v>1352.282146799542</v>
+        <v>1356.597155879224</v>
       </c>
       <c r="J154">
-        <v>2413.10420873392</v>
+        <v>2423.339796959543</v>
       </c>
       <c r="K154">
-        <v>2896.272624473197</v>
+        <v>2903.807850601258</v>
       </c>
       <c r="L154">
-        <v>2354.896167539528</v>
+        <v>2361.063203457704</v>
       </c>
       <c r="M154">
-        <v>3449.239230262674</v>
+        <v>3455.19650656727</v>
       </c>
     </row>
     <row r="155">
@@ -7949,22 +7949,22 @@
         <v>1052.020966476623</v>
       </c>
       <c r="H155">
-        <v>1393.225483508281</v>
+        <v>1551.151438423097</v>
       </c>
       <c r="I155">
-        <v>912.4440591413311</v>
+        <v>1019.108633332983</v>
       </c>
       <c r="J155">
-        <v>1901.682143271235</v>
+        <v>2113.154577257312</v>
       </c>
       <c r="K155">
-        <v>2349.381760081003</v>
+        <v>2507.309672193794</v>
       </c>
       <c r="L155">
-        <v>1856.523220362247</v>
+        <v>1958.126012811259</v>
       </c>
       <c r="M155">
-        <v>2863.875130833347</v>
+        <v>3076.864836499257</v>
       </c>
     </row>
     <row r="156">
@@ -7998,22 +7998,22 @@
         <v>1163.311380537882</v>
       </c>
       <c r="H156">
-        <v>1592.098825533483</v>
+        <v>1592.328503750295</v>
       </c>
       <c r="I156">
-        <v>1108.608632633127</v>
+        <v>1111.036491264603</v>
       </c>
       <c r="J156">
-        <v>2098.619417665167</v>
+        <v>2095.961217611786</v>
       </c>
       <c r="K156">
-        <v>2642.404987306488</v>
+        <v>2644.364181381612</v>
       </c>
       <c r="L156">
-        <v>2148.390129297505</v>
+        <v>2146.124746541923</v>
       </c>
       <c r="M156">
-        <v>3166.166476020646</v>
+        <v>3166.948165704256</v>
       </c>
     </row>
     <row r="157">
@@ -8047,22 +8047,22 @@
         <v>1267.992124088338</v>
       </c>
       <c r="H157">
-        <v>1473.572474622909</v>
+        <v>1804.841288058519</v>
       </c>
       <c r="I157">
-        <v>962.7954398328609</v>
+        <v>1149.607879830401</v>
       </c>
       <c r="J157">
-        <v>1990.944713824485</v>
+        <v>2468.767611478587</v>
       </c>
       <c r="K157">
-        <v>2628.056728549032</v>
+        <v>2960.081605197137</v>
       </c>
       <c r="L157">
-        <v>2106.591506704796</v>
+        <v>2289.221921232226</v>
       </c>
       <c r="M157">
-        <v>3158.757492258864</v>
+        <v>3625.806217426919</v>
       </c>
     </row>
     <row r="158">
@@ -8096,22 +8096,22 @@
         <v>572.4069357732404</v>
       </c>
       <c r="H158">
-        <v>1473.077687362382</v>
+        <v>1501.598338422675</v>
       </c>
       <c r="I158">
-        <v>1011.510575718305</v>
+        <v>1008.716303496127</v>
       </c>
       <c r="J158">
-        <v>1945.291149587793</v>
+        <v>2001.563872939575</v>
       </c>
       <c r="K158">
-        <v>1954.8551673081</v>
+        <v>1982.315424688028</v>
       </c>
       <c r="L158">
-        <v>1485.055588030646</v>
+        <v>1486.056336232127</v>
       </c>
       <c r="M158">
-        <v>2439.519134173562</v>
+        <v>2496.526356429187</v>
       </c>
     </row>
     <row r="159">
@@ -8145,22 +8145,22 @@
         <v>742.0928382185882</v>
       </c>
       <c r="H159">
-        <v>2563.036462228165</v>
+        <v>2430.352965443918</v>
       </c>
       <c r="I159">
-        <v>1507.46744512475</v>
+        <v>1560.696649978984</v>
       </c>
       <c r="J159">
-        <v>3706.771882298122</v>
+        <v>3354.732952099554</v>
       </c>
       <c r="K159">
-        <v>3197.577514119552</v>
+        <v>3068.603758083784</v>
       </c>
       <c r="L159">
-        <v>2156.694073245343</v>
+        <v>2195.692355827876</v>
       </c>
       <c r="M159">
-        <v>4341.356091352304</v>
+        <v>3994.929245840062</v>
       </c>
     </row>
     <row r="160">
@@ -8194,22 +8194,22 @@
         <v>678.4292995591759</v>
       </c>
       <c r="H160">
-        <v>1535.365064123297</v>
+        <v>1549.928886864782</v>
       </c>
       <c r="I160">
-        <v>1194.594456933893</v>
+        <v>1201.590442108513</v>
       </c>
       <c r="J160">
-        <v>1868.026751835574</v>
+        <v>1892.391549179404</v>
       </c>
       <c r="K160">
-        <v>2145.386755246534</v>
+        <v>2159.559121364479</v>
       </c>
       <c r="L160">
-        <v>1795.530157229345</v>
+        <v>1801.589844433998</v>
       </c>
       <c r="M160">
-        <v>2484.760765239173</v>
+        <v>2507.284622576514</v>
       </c>
     </row>
     <row r="161">
@@ -8243,22 +8243,22 @@
         <v>746.9645416971471</v>
       </c>
       <c r="H161">
-        <v>1368.656175120461</v>
+        <v>1524.40462404604</v>
       </c>
       <c r="I161">
-        <v>1001.120894172463</v>
+        <v>1129.481523522449</v>
       </c>
       <c r="J161">
-        <v>1744.688786837274</v>
+        <v>1926.566449700377</v>
       </c>
       <c r="K161">
-        <v>2045.031833984922</v>
+        <v>2201.710444815298</v>
       </c>
       <c r="L161">
-        <v>1670.3125035649</v>
+        <v>1798.462478875222</v>
       </c>
       <c r="M161">
-        <v>2427.282857051121</v>
+        <v>2613.162485801137</v>
       </c>
     </row>
     <row r="162">
@@ -8292,22 +8292,22 @@
         <v>2025.912452024941</v>
       </c>
       <c r="H162">
-        <v>1436.385109620416</v>
+        <v>1447.088220019286</v>
       </c>
       <c r="I162">
-        <v>1055.416609460065</v>
+        <v>1063.847031554879</v>
       </c>
       <c r="J162">
-        <v>1809.827573808297</v>
+        <v>1825.587570247771</v>
       </c>
       <c r="K162">
-        <v>3263.458363454703</v>
+        <v>3273.955164921113</v>
       </c>
       <c r="L162">
-        <v>2830.95795009118</v>
+        <v>2839.126395277015</v>
       </c>
       <c r="M162">
-        <v>3687.035906560214</v>
+        <v>3702.391796121453</v>
       </c>
     </row>
     <row r="163">
@@ -8341,22 +8341,22 @@
         <v>2130.904865267277</v>
       </c>
       <c r="H163">
-        <v>1994.695443599301</v>
+        <v>2158.51782771718</v>
       </c>
       <c r="I163">
-        <v>1409.118762900385</v>
+        <v>1534.84698833795</v>
       </c>
       <c r="J163">
-        <v>2613.91375111709</v>
+        <v>2785.800757187139</v>
       </c>
       <c r="K163">
-        <v>3920.679622876534</v>
+        <v>4082.909688311075</v>
       </c>
       <c r="L163">
-        <v>3294.828203069129</v>
+        <v>3427.301912466759</v>
       </c>
       <c r="M163">
-        <v>4559.13204348072</v>
+        <v>4739.581535367583</v>
       </c>
     </row>
     <row r="164">
@@ -8390,22 +8390,22 @@
         <v>537.2450400597623</v>
       </c>
       <c r="H164">
-        <v>1157.368666180786</v>
+        <v>1174.218104647835</v>
       </c>
       <c r="I164">
-        <v>836.6403061909137</v>
+        <v>847.9110002418445</v>
       </c>
       <c r="J164">
-        <v>1485.816624798304</v>
+        <v>1506.717316192678</v>
       </c>
       <c r="K164">
-        <v>1611.173903532</v>
+        <v>1627.612205808686</v>
       </c>
       <c r="L164">
-        <v>1278.782436782103</v>
+        <v>1288.845685141338</v>
       </c>
       <c r="M164">
-        <v>1948.951468783785</v>
+        <v>1971.049212133563</v>
       </c>
     </row>
     <row r="165">
@@ -8439,22 +8439,22 @@
         <v>617.4403129457854</v>
       </c>
       <c r="H165">
-        <v>1435.643072890389</v>
+        <v>1582.730017127354</v>
       </c>
       <c r="I165">
-        <v>930.9983093350615</v>
+        <v>1036.177848145073</v>
       </c>
       <c r="J165">
-        <v>1992.606823368748</v>
+        <v>2165.078216323715</v>
       </c>
       <c r="K165">
-        <v>1959.696442414774</v>
+        <v>2105.902634347914</v>
       </c>
       <c r="L165">
-        <v>1441.457098474756</v>
+        <v>1549.893588203075</v>
       </c>
       <c r="M165">
-        <v>2526.565171880397</v>
+        <v>2695.598836166615</v>
       </c>
     </row>
     <row r="166">
@@ -8488,22 +8488,22 @@
         <v>488.2093824866313</v>
       </c>
       <c r="H166">
-        <v>1112.894814548843</v>
+        <v>1100.600770138349</v>
       </c>
       <c r="I166">
-        <v>757.8996363307197</v>
+        <v>748.4681080544989</v>
       </c>
       <c r="J166">
-        <v>1467.541768023979</v>
+        <v>1450.703379321926</v>
       </c>
       <c r="K166">
-        <v>1507.574516156878</v>
+        <v>1494.118243570436</v>
       </c>
       <c r="L166">
-        <v>1138.24387521199</v>
+        <v>1125.272063003516</v>
       </c>
       <c r="M166">
-        <v>1872.619467406023</v>
+        <v>1857.794108377379</v>
       </c>
     </row>
     <row r="167">
@@ -8537,22 +8537,22 @@
         <v>549.3428309896404</v>
       </c>
       <c r="H167">
-        <v>1728.273606638164</v>
+        <v>1977.375080739157</v>
       </c>
       <c r="I167">
-        <v>1142.909124449486</v>
+        <v>1312.655234647945</v>
       </c>
       <c r="J167">
-        <v>2324.196216356118</v>
+        <v>2642.939350261932</v>
       </c>
       <c r="K167">
-        <v>2171.815055941488</v>
+        <v>2419.726133394141</v>
       </c>
       <c r="L167">
-        <v>1578.395130936667</v>
+        <v>1753.185289658702</v>
       </c>
       <c r="M167">
-        <v>2767.15580193352</v>
+        <v>3084.008181931435</v>
       </c>
     </row>
     <row r="168">
@@ -8586,22 +8586,22 @@
         <v>984.6335212651525</v>
       </c>
       <c r="H168">
-        <v>1757.605723463438</v>
+        <v>1783.282414922994</v>
       </c>
       <c r="I168">
-        <v>1250.948487968287</v>
+        <v>1264.784152624907</v>
       </c>
       <c r="J168">
-        <v>2290.194412884617</v>
+        <v>2322.831568284108</v>
       </c>
       <c r="K168">
-        <v>2582.047260491624</v>
+        <v>2608.221163304889</v>
       </c>
       <c r="L168">
-        <v>2044.711272238438</v>
+        <v>2061.117230522868</v>
       </c>
       <c r="M168">
-        <v>3138.086084132629</v>
+        <v>3171.161704154093</v>
       </c>
     </row>
     <row r="169">
@@ -8635,22 +8635,22 @@
         <v>1337.061599462393</v>
       </c>
       <c r="H169">
-        <v>2205.571259944948</v>
+        <v>2756.560506154912</v>
       </c>
       <c r="I169">
-        <v>1381.71336819884</v>
+        <v>1725.353031584411</v>
       </c>
       <c r="J169">
-        <v>3074.70436071099</v>
+        <v>3846.966121231647</v>
       </c>
       <c r="K169">
-        <v>3348.775724455033</v>
+        <v>3900.830575659266</v>
       </c>
       <c r="L169">
-        <v>2500.103534769658</v>
+        <v>2842.722163536819</v>
       </c>
       <c r="M169">
-        <v>4242.481067351933</v>
+        <v>5009.099652274886</v>
       </c>
     </row>
     <row r="170">
@@ -8684,22 +8684,22 @@
         <v>798.5544466797739</v>
       </c>
       <c r="H170">
-        <v>1261.113160613856</v>
+        <v>1235.959105686365</v>
       </c>
       <c r="I170">
-        <v>893.8105045808205</v>
+        <v>878.7257633457081</v>
       </c>
       <c r="J170">
-        <v>1643.773128368779</v>
+        <v>1600.714956874793</v>
       </c>
       <c r="K170">
-        <v>2001.335034346169</v>
+        <v>1975.011819891692</v>
       </c>
       <c r="L170">
-        <v>1631.316571967361</v>
+        <v>1616.394160577213</v>
       </c>
       <c r="M170">
-        <v>2387.556666189572</v>
+        <v>2349.673948980396</v>
       </c>
     </row>
     <row r="171">
@@ -8733,22 +8733,22 @@
         <v>835.8183887884974</v>
       </c>
       <c r="H171">
-        <v>2193.594068652122</v>
+        <v>2539.348620928022</v>
       </c>
       <c r="I171">
-        <v>1523.398547007348</v>
+        <v>1751.756099021334</v>
       </c>
       <c r="J171">
-        <v>2860.897147732823</v>
+        <v>3323.681095982647</v>
       </c>
       <c r="K171">
-        <v>2967.208514034144</v>
+        <v>3310.339121104884</v>
       </c>
       <c r="L171">
-        <v>2298.368019179069</v>
+        <v>2525.661412541263</v>
       </c>
       <c r="M171">
-        <v>3637.091904286224</v>
+        <v>4103.144922385393</v>
       </c>
     </row>
     <row r="172">
@@ -8782,22 +8782,22 @@
         <v>1365.860572981189</v>
       </c>
       <c r="H172">
-        <v>1703.864391046694</v>
+        <v>1735.253332051868</v>
       </c>
       <c r="I172">
-        <v>1249.928110487219</v>
+        <v>1276.404145824136</v>
       </c>
       <c r="J172">
-        <v>2209.517018964692</v>
+        <v>2248.176438060946</v>
       </c>
       <c r="K172">
-        <v>2955.510230335997</v>
+        <v>2986.192536509851</v>
       </c>
       <c r="L172">
-        <v>2484.088156744056</v>
+        <v>2506.564151025592</v>
       </c>
       <c r="M172">
-        <v>3480.93295860627</v>
+        <v>3517.060360964099</v>
       </c>
     </row>
     <row r="173">
@@ -8831,22 +8831,22 @@
         <v>1320.340751800204</v>
       </c>
       <c r="H173">
-        <v>1347.111419185158</v>
+        <v>1657.349807353177</v>
       </c>
       <c r="I173">
-        <v>900.0816147476638</v>
+        <v>1127.830403430579</v>
       </c>
       <c r="J173">
-        <v>1856.312740339148</v>
+        <v>2255.130282231461</v>
       </c>
       <c r="K173">
-        <v>2559.499360173508</v>
+        <v>2867.748336487646</v>
       </c>
       <c r="L173">
-        <v>2097.22680141831</v>
+        <v>2322.850641334849</v>
       </c>
       <c r="M173">
-        <v>3071.387999172788</v>
+        <v>3465.185849358087</v>
       </c>
     </row>
     <row r="174">
@@ -8880,22 +8880,22 @@
         <v>1368.096981732356</v>
       </c>
       <c r="H174">
-        <v>2134.497899517638</v>
+        <v>2132.508704920439</v>
       </c>
       <c r="I174">
-        <v>1541.993281871128</v>
+        <v>1534.686207086381</v>
       </c>
       <c r="J174">
-        <v>2737.120669039816</v>
+        <v>2741.286665868768</v>
       </c>
       <c r="K174">
-        <v>3360.425929464568</v>
+        <v>3357.711781383372</v>
       </c>
       <c r="L174">
-        <v>2746.931748610727</v>
+        <v>2736.950690127112</v>
       </c>
       <c r="M174">
-        <v>3988.358641976885</v>
+        <v>3992.170908221774</v>
       </c>
     </row>
     <row r="175">
@@ -8929,22 +8929,22 @@
         <v>1384.829419927487</v>
       </c>
       <c r="H175">
-        <v>1671.465908545438</v>
+        <v>2023.119399486449</v>
       </c>
       <c r="I175">
-        <v>1009.704140185498</v>
+        <v>1236.99152232372</v>
       </c>
       <c r="J175">
-        <v>2380.604131529165</v>
+        <v>2856.714854763001</v>
       </c>
       <c r="K175">
-        <v>2924.424593761007</v>
+        <v>3276.648204209624</v>
       </c>
       <c r="L175">
-        <v>2250.733485319518</v>
+        <v>2483.383036380084</v>
       </c>
       <c r="M175">
-        <v>3643.733852535784</v>
+        <v>4125.766275282096</v>
       </c>
     </row>
     <row r="176">
@@ -8978,22 +8978,22 @@
         <v>525.1684685023889</v>
       </c>
       <c r="H176">
-        <v>1529.103512209343</v>
+        <v>1552.792480156846</v>
       </c>
       <c r="I176">
-        <v>1142.781979544864</v>
+        <v>1141.290794883766</v>
       </c>
       <c r="J176">
-        <v>1922.627669785241</v>
+        <v>1963.577323719654</v>
       </c>
       <c r="K176">
-        <v>1978.082034879225</v>
+        <v>2001.407672517372</v>
       </c>
       <c r="L176">
-        <v>1580.738798514396</v>
+        <v>1582.345587210327</v>
       </c>
       <c r="M176">
-        <v>2374.111570429466</v>
+        <v>2414.606601898858</v>
       </c>
     </row>
     <row r="177">
@@ -9027,22 +9027,22 @@
         <v>683.2430653387103</v>
       </c>
       <c r="H177">
-        <v>1794.201128176791</v>
+        <v>2101.902536642566</v>
       </c>
       <c r="I177">
-        <v>1306.444486522306</v>
+        <v>1534.304527561323</v>
       </c>
       <c r="J177">
-        <v>2291.597168403211</v>
+        <v>2671.311879161197</v>
       </c>
       <c r="K177">
-        <v>2391.581391534995</v>
+        <v>2697.44628216458</v>
       </c>
       <c r="L177">
-        <v>1893.151822594444</v>
+        <v>2122.301929132171</v>
       </c>
       <c r="M177">
-        <v>2890.128527139473</v>
+        <v>3277.167702024413</v>
       </c>
     </row>
     <row r="178">
@@ -9076,22 +9076,22 @@
         <v>995.2816670961778</v>
       </c>
       <c r="H178">
-        <v>1614.721862458898</v>
+        <v>1627.989306461739</v>
       </c>
       <c r="I178">
-        <v>1218.084006959734</v>
+        <v>1227.877289085441</v>
       </c>
       <c r="J178">
-        <v>2021.767105280524</v>
+        <v>2036.98546524218</v>
       </c>
       <c r="K178">
-        <v>2519.496593329754</v>
+        <v>2531.306741350932</v>
       </c>
       <c r="L178">
-        <v>2110.654452441962</v>
+        <v>2121.564964757407</v>
       </c>
       <c r="M178">
-        <v>2939.680138332109</v>
+        <v>2954.843496720411</v>
       </c>
     </row>
     <row r="179">
@@ -9125,22 +9125,22 @@
         <v>1044.896096510061</v>
       </c>
       <c r="H179">
-        <v>1660.411602172549</v>
+        <v>1733.704753566527</v>
       </c>
       <c r="I179">
-        <v>1128.608423241622</v>
+        <v>1229.347996958521</v>
       </c>
       <c r="J179">
-        <v>2247.442670100193</v>
+        <v>2252.726911174143</v>
       </c>
       <c r="K179">
-        <v>2612.30583698552</v>
+        <v>2683.992139005169</v>
       </c>
       <c r="L179">
-        <v>2069.004575047565</v>
+        <v>2165.13631583236</v>
       </c>
       <c r="M179">
-        <v>3200.112989073252</v>
+        <v>3205.447857198137</v>
       </c>
     </row>
     <row r="180">
@@ -9174,22 +9174,22 @@
         <v>1230.086500608997</v>
       </c>
       <c r="H180">
-        <v>2082.783416226807</v>
+        <v>2081.004323302191</v>
       </c>
       <c r="I180">
-        <v>1564.454658246461</v>
+        <v>1556.933974436784</v>
       </c>
       <c r="J180">
-        <v>2591.522186061025</v>
+        <v>2596.569007892221</v>
       </c>
       <c r="K180">
-        <v>3196.159889248397</v>
+        <v>3194.692084613278</v>
       </c>
       <c r="L180">
-        <v>2657.623898809493</v>
+        <v>2649.278705680928</v>
       </c>
       <c r="M180">
-        <v>3718.554464189494</v>
+        <v>3716.269750061012</v>
       </c>
     </row>
     <row r="181">
@@ -9223,22 +9223,22 @@
         <v>1126.872136602683</v>
       </c>
       <c r="H181">
-        <v>2403.987875470854</v>
+        <v>2689.225463511179</v>
       </c>
       <c r="I181">
-        <v>1575.218498703322</v>
+        <v>1753.607243150487</v>
       </c>
       <c r="J181">
-        <v>3246.769141893579</v>
+        <v>3622.108375152216</v>
       </c>
       <c r="K181">
-        <v>3417.235505881245</v>
+        <v>3699.330299139526</v>
       </c>
       <c r="L181">
-        <v>2579.963669372557</v>
+        <v>2763.908129396538</v>
       </c>
       <c r="M181">
-        <v>4257.351803776305</v>
+        <v>4641.772872732967</v>
       </c>
     </row>
     <row r="182">
@@ -9272,22 +9272,22 @@
         <v>643.9311604741748</v>
       </c>
       <c r="H182">
-        <v>1834.125082792206</v>
+        <v>1810.843289479136</v>
       </c>
       <c r="I182">
-        <v>1404.768071074821</v>
+        <v>1387.242865575561</v>
       </c>
       <c r="J182">
-        <v>2272.50657418155</v>
+        <v>2244.741400811653</v>
       </c>
       <c r="K182">
-        <v>2376.585130187097</v>
+        <v>2355.231041524105</v>
       </c>
       <c r="L182">
-        <v>1932.563617266505</v>
+        <v>1918.088798965886</v>
       </c>
       <c r="M182">
-        <v>2828.112675372545</v>
+        <v>2797.387468199216</v>
       </c>
     </row>
     <row r="183">
@@ -9321,22 +9321,22 @@
         <v>726.1124548215233</v>
       </c>
       <c r="H183">
-        <v>2984.065830267665</v>
+        <v>3426.541006989672</v>
       </c>
       <c r="I183">
-        <v>2146.886480592074</v>
+        <v>2469.172012677565</v>
       </c>
       <c r="J183">
-        <v>3825.458592488342</v>
+        <v>4362.330630322454</v>
       </c>
       <c r="K183">
-        <v>3607.921321122277</v>
+        <v>4049.732796711511</v>
       </c>
       <c r="L183">
-        <v>2757.778651635826</v>
+        <v>3076.83980664887</v>
       </c>
       <c r="M183">
-        <v>4459.102146606783</v>
+        <v>4989.4008003868</v>
       </c>
     </row>
     <row r="184">
@@ -9370,22 +9370,22 @@
         <v>1453.442775623383</v>
       </c>
       <c r="H184">
-        <v>1952.080176341874</v>
+        <v>1951.777655885706</v>
       </c>
       <c r="I184">
-        <v>1312.517570902801</v>
+        <v>1290.25167304726</v>
       </c>
       <c r="J184">
-        <v>2627.41264947945</v>
+        <v>2637.969673839428</v>
       </c>
       <c r="K184">
-        <v>3186.819292574386</v>
+        <v>3185.470956454477</v>
       </c>
       <c r="L184">
-        <v>2509.135393473789</v>
+        <v>2493.047624507532</v>
       </c>
       <c r="M184">
-        <v>3895.432385603568</v>
+        <v>3903.418603511979</v>
       </c>
     </row>
     <row r="185">
@@ -9419,22 +9419,22 @@
         <v>1350.525872725603</v>
       </c>
       <c r="H185">
-        <v>3070.376773715383</v>
+        <v>3553.725253853791</v>
       </c>
       <c r="I185">
-        <v>1904.543965145368</v>
+        <v>2203.06860447192</v>
       </c>
       <c r="J185">
-        <v>4335.982667549922</v>
+        <v>4995.523387365422</v>
       </c>
       <c r="K185">
-        <v>4224.279313839237</v>
+        <v>4704.774914395297</v>
       </c>
       <c r="L185">
-        <v>3046.577690635061</v>
+        <v>3359.824116821082</v>
       </c>
       <c r="M185">
-        <v>5490.860451249251</v>
+        <v>6152.400960525429</v>
       </c>
     </row>
     <row r="186">
@@ -9468,22 +9468,22 @@
         <v>433.5909007177058</v>
       </c>
       <c r="H186">
-        <v>1416.965686343023</v>
+        <v>1441.00775965075</v>
       </c>
       <c r="I186">
-        <v>1068.749070866354</v>
+        <v>1084.549686397555</v>
       </c>
       <c r="J186">
-        <v>1763.474429564099</v>
+        <v>1795.885768809591</v>
       </c>
       <c r="K186">
-        <v>1820.085436205987</v>
+        <v>1842.083766733279</v>
       </c>
       <c r="L186">
-        <v>1467.962594079019</v>
+        <v>1487.270683291249</v>
       </c>
       <c r="M186">
-        <v>2169.05709727523</v>
+        <v>2198.98093421577</v>
       </c>
     </row>
     <row r="187">
@@ -9517,22 +9517,22 @@
         <v>554.2768617891048</v>
       </c>
       <c r="H187">
-        <v>2172.519870502083</v>
+        <v>2500.732036918744</v>
       </c>
       <c r="I187">
-        <v>1613.214688690166</v>
+        <v>1831.987887907389</v>
       </c>
       <c r="J187">
-        <v>2769.188605619465</v>
+        <v>3195.180018800533</v>
       </c>
       <c r="K187">
-        <v>2688.898630996498</v>
+        <v>3014.877650553413</v>
       </c>
       <c r="L187">
-        <v>2125.651457141073</v>
+        <v>2346.314234539358</v>
       </c>
       <c r="M187">
-        <v>3291.165280590453</v>
+        <v>3713.706619172461</v>
       </c>
     </row>
     <row r="188">
@@ -9566,22 +9566,22 @@
         <v>733.6218052757374</v>
       </c>
       <c r="H188">
-        <v>1300.350893432851</v>
+        <v>1295.578080753741</v>
       </c>
       <c r="I188">
-        <v>864.5905561251419</v>
+        <v>857.6489949865829</v>
       </c>
       <c r="J188">
-        <v>1743.724329103778</v>
+        <v>1737.389551306246</v>
       </c>
       <c r="K188">
-        <v>1937.577680923407</v>
+        <v>1932.831237642644</v>
       </c>
       <c r="L188">
-        <v>1490.397068153432</v>
+        <v>1484.532966717936</v>
       </c>
       <c r="M188">
-        <v>2386.228573297145</v>
+        <v>2382.011986201285</v>
       </c>
     </row>
     <row r="189">
@@ -9615,22 +9615,22 @@
         <v>730.4519294887635</v>
       </c>
       <c r="H189">
-        <v>1964.151806682174</v>
+        <v>2080.323497641359</v>
       </c>
       <c r="I189">
-        <v>1274.774824062669</v>
+        <v>1395.704564230794</v>
       </c>
       <c r="J189">
-        <v>2720.989766898663</v>
+        <v>2799.690659106749</v>
       </c>
       <c r="K189">
-        <v>2603.441367699319</v>
+        <v>2716.712840419235</v>
       </c>
       <c r="L189">
-        <v>1900.772278082002</v>
+        <v>2025.042675761241</v>
       </c>
       <c r="M189">
-        <v>3356.453840717615</v>
+        <v>3449.573179101124</v>
       </c>
     </row>
     <row r="190">
@@ -9664,22 +9664,22 @@
         <v>759.9118959759799</v>
       </c>
       <c r="H190">
-        <v>1454.24709081721</v>
+        <v>1441.139563578827</v>
       </c>
       <c r="I190">
-        <v>1108.072530160785</v>
+        <v>1095.822585465243</v>
       </c>
       <c r="J190">
-        <v>1812.211559720946</v>
+        <v>1796.174267640456</v>
       </c>
       <c r="K190">
-        <v>2144.708051938117</v>
+        <v>2131.447211571379</v>
       </c>
       <c r="L190">
-        <v>1792.17639399111</v>
+        <v>1783.306974374175</v>
       </c>
       <c r="M190">
-        <v>2510.608211815695</v>
+        <v>2494.223688059277</v>
       </c>
     </row>
     <row r="191">
@@ -9713,22 +9713,22 @@
         <v>819.422130926166</v>
       </c>
       <c r="H191">
-        <v>1811.180997606352</v>
+        <v>2142.605481424013</v>
       </c>
       <c r="I191">
-        <v>1222.498615941046</v>
+        <v>1415.678112127506</v>
       </c>
       <c r="J191">
-        <v>2420.596653950251</v>
+        <v>2872.897114083923</v>
       </c>
       <c r="K191">
-        <v>2558.916929761027</v>
+        <v>2891.227487750363</v>
       </c>
       <c r="L191">
-        <v>1961.085604057379</v>
+        <v>2160.681951835003</v>
       </c>
       <c r="M191">
-        <v>3169.797868666877</v>
+        <v>3631.686694579722</v>
       </c>
     </row>
     <row r="192">
@@ -9762,22 +9762,22 @@
         <v>872.9833367425206</v>
       </c>
       <c r="H192">
-        <v>1950.072759191964</v>
+        <v>1984.106173756714</v>
       </c>
       <c r="I192">
-        <v>1178.507877464704</v>
+        <v>1180.82962636566</v>
       </c>
       <c r="J192">
-        <v>2771.277779102417</v>
+        <v>2837.675917049305</v>
       </c>
       <c r="K192">
-        <v>2588.555309621307</v>
+        <v>2622.41326734064</v>
       </c>
       <c r="L192">
-        <v>1779.767459946412</v>
+        <v>1787.002247192982</v>
       </c>
       <c r="M192">
-        <v>3442.238215599403</v>
+        <v>3510.198301687521</v>
       </c>
     </row>
     <row r="193">
@@ -9811,22 +9811,22 @@
         <v>1068.522749159751</v>
       </c>
       <c r="H193">
-        <v>3726.828353765452</v>
+        <v>4022.620017989632</v>
       </c>
       <c r="I193">
-        <v>2134.5843985174</v>
+        <v>2325.654906464757</v>
       </c>
       <c r="J193">
-        <v>5583.796627690736</v>
+        <v>5960.673486921445</v>
       </c>
       <c r="K193">
-        <v>4553.417513738399</v>
+        <v>4854.246178264695</v>
       </c>
       <c r="L193">
-        <v>2941.142093079634</v>
+        <v>3139.778138560001</v>
       </c>
       <c r="M193">
-        <v>6409.48626485073</v>
+        <v>6833.274634675608</v>
       </c>
     </row>
   </sheetData>
